--- a/backend/app/assets/kpi/kpi-template-vn.xlsx
+++ b/backend/app/assets/kpi/kpi-template-vn.xlsx
@@ -8,13 +8,14 @@
   <sheets>
     <sheet name="KPI Operator Demo" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="KPI QA Demo " sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="KPI Developer Demo" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="QA_tiêu chí A_full " sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Operator_tiêu chí A_full" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Developer_tiêu chí A_full" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Trang_tính1" sheetId="7" state="hidden" r:id="rId7"/>
-    <sheet name="Bảng tiêu chí B,C" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Kế hoạch Developer" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="KPI Lead Developer Demo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="KPI Developer Demo" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="QA_tiêu chí A_full " sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Operator_tiêu chí A_full" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Developer_tiêu chí A_full" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Trang_tính1" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet name="Bảng tiêu chí B,C" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Kế hoạch Developer" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -30,7 +31,7 @@
     <numFmt numFmtId="167" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="168" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="58">
+  <fonts count="79">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -437,8 +438,153 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <b val="1"/>
+      <color theme="0"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <b val="1"/>
+      <color rgb="FF222222"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <b val="1"/>
+      <color rgb="FFFF0000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <color rgb="FF222222"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <b val="1"/>
+      <color theme="0"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <charset val="163"/>
+      <family val="1"/>
+      <b val="1"/>
+      <color theme="0"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <charset val="163"/>
+      <family val="1"/>
+      <b val="1"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="14"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="14"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="16"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="43">
+  <fills count="45">
     <fill>
       <patternFill/>
     </fill>
@@ -691,8 +837,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.3999755851924192"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.7999816888943144"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="39">
+  <borders count="51">
     <border>
       <left/>
       <right/>
@@ -1138,6 +1296,144 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0"/>
@@ -1285,7 +1581,7 @@
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="315">
+  <cellXfs count="468">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2177,6 +2473,457 @@
     </xf>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="4" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="4" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="4" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="4" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="58" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="58" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="11" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="11" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="11" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="61" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="11" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="60" fillId="11" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="9" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="9" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="60" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="9" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="61" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="63" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="63" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="64" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="64" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="3" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="63" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="63" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="63" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="63" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="9" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="9" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="61" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="63" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="63" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="9" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="3" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="63" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="9" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="9" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="63" fillId="9" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="9" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="9" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="63" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="11" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="11" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="60" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="60" fillId="11" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="60" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="11" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="11" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="60" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="69" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="69" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="63" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="61" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="61" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="63" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="63" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="70" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="11" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="60" fillId="11" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="11" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="61" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="11" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="61" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="63" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="63" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="63" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="4" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="58" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="71" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="71" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="64" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="72" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="72" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="43" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="43" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="75" fillId="43" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="44" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="44" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="76" fillId="44" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="44" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="44" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="76" fillId="44" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="78" fillId="44" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4531,6 +5278,88 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="4"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Điền 1 mã Jira trên mỗi dòng. Loại kế hoạch: Cam kết | Phát sinh | Ngoài phạm vi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="313" t="inlineStr">
+        <is>
+          <t>Mã Jira</t>
+        </is>
+      </c>
+      <c r="B2" s="313" t="inlineStr">
+        <is>
+          <t>Tên công việc</t>
+        </is>
+      </c>
+      <c r="C2" s="313" t="inlineStr">
+        <is>
+          <t>Loại kế hoạch</t>
+        </is>
+      </c>
+      <c r="D2" s="313" t="inlineStr">
+        <is>
+          <t>Hạn dự kiến</t>
+        </is>
+      </c>
+      <c r="E2" s="313" t="inlineStr">
+        <is>
+          <t>Điểm khối lượng</t>
+        </is>
+      </c>
+      <c r="F2" s="313" t="inlineStr">
+        <is>
+          <t>Ghi chú / lý do loại trừ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="D3" s="314" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="314" t="n"/>
+    </row>
+    <row r="5" ht="28.5" customHeight="1">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="D5" s="314" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C3:C300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Cam kết,Phát sinh,Ngoài phạm vi"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -5979,66 +6808,65 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FFFF0000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T28"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.142857142857141" defaultRowHeight="15"/>
+  <dimension ref="A1:T38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9.142857142857141" customWidth="1" style="122" min="1" max="1"/>
-    <col width="37.2857142857143" customWidth="1" min="2" max="2"/>
-    <col width="19.1428571428571" customWidth="1" min="3" max="3"/>
-    <col width="17.7142857142857" customWidth="1" min="4" max="4"/>
-    <col width="67.71428571428569" customWidth="1" min="5" max="5"/>
-    <col width="46.7142857142857" customWidth="1" min="6" max="6"/>
-    <col width="36.1428571428571" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" style="122" min="8" max="9"/>
-    <col width="18.7142857142857" customWidth="1" style="122" min="10" max="10"/>
-    <col width="27.4285714285714" customWidth="1" style="122" min="11" max="11"/>
-    <col width="18.2857142857143" customWidth="1" style="122" min="12" max="12"/>
-    <col width="18.4285714285714" customWidth="1" style="122" min="13" max="13"/>
-    <col width="17.7142857142857" customWidth="1" style="122" min="14" max="14"/>
-    <col width="35.4285714285714" customWidth="1" style="122" min="15" max="15"/>
+    <col width="9.140625" customWidth="1" min="1" max="1"/>
+    <col width="37.28515625" customWidth="1" min="2" max="2"/>
+    <col width="19.140625" customWidth="1" min="3" max="3"/>
+    <col width="17.7109375" customWidth="1" min="4" max="4"/>
+    <col width="67.7109375" customWidth="1" min="5" max="5"/>
+    <col width="46.7109375" customWidth="1" min="6" max="6"/>
+    <col width="36.140625" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18.7109375" customWidth="1" min="10" max="10"/>
+    <col width="27.42578125" customWidth="1" min="11" max="11"/>
+    <col width="18.28515625" customWidth="1" min="12" max="12"/>
+    <col width="18.42578125" customWidth="1" min="13" max="13"/>
+    <col width="17.7109375" customWidth="1" min="14" max="14"/>
+    <col width="35.42578125" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1">
-      <c r="A1" s="123" t="inlineStr">
+      <c r="A1" s="315" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B1" s="123" t="inlineStr">
+      <c r="B1" s="315" t="inlineStr">
         <is>
           <t>CHỈ TIÊU</t>
         </is>
       </c>
-      <c r="C1" s="123" t="inlineStr">
+      <c r="C1" s="315" t="inlineStr">
         <is>
           <t>Kế hoạch (Điểm)</t>
         </is>
       </c>
-      <c r="D1" s="123" t="inlineStr">
+      <c r="D1" s="315" t="inlineStr">
         <is>
           <t>Trọng số</t>
         </is>
       </c>
-      <c r="E1" s="124" t="inlineStr">
+      <c r="E1" s="316" t="inlineStr">
         <is>
           <t>MÔ TẢ THƯỚC ĐO CHỈ TIÊU</t>
         </is>
       </c>
-      <c r="F1" s="125" t="inlineStr">
+      <c r="F1" s="317" t="inlineStr">
         <is>
           <t>Công thức Tính</t>
         </is>
       </c>
-      <c r="G1" s="125" t="inlineStr">
+      <c r="G1" s="317" t="inlineStr">
         <is>
           <t>Công thức Tính (Thang điểm 10)</t>
         </is>
       </c>
-      <c r="H1" s="126" t="inlineStr">
+      <c r="H1" s="318" t="inlineStr">
         <is>
           <t>NHÂN VIÊN ĐÁNH GIÁ</t>
         </is>
@@ -6046,7 +6874,7 @@
       <c r="I1" s="127" t="n"/>
       <c r="J1" s="127" t="n"/>
       <c r="K1" s="27" t="n"/>
-      <c r="L1" s="126" t="inlineStr">
+      <c r="L1" s="318" t="inlineStr">
         <is>
           <t>CBQL ĐÁNH GIÁ</t>
         </is>
@@ -6054,161 +6882,161 @@
       <c r="M1" s="127" t="n"/>
       <c r="N1" s="127" t="n"/>
       <c r="O1" s="27" t="n"/>
-      <c r="P1" s="128" t="n"/>
-      <c r="Q1" s="128" t="n"/>
-      <c r="R1" s="128" t="n"/>
-      <c r="S1" s="128" t="n"/>
+      <c r="P1" s="319" t="n"/>
+      <c r="Q1" s="319" t="n"/>
+      <c r="R1" s="319" t="n"/>
+      <c r="S1" s="319" t="n"/>
     </row>
     <row r="2" ht="61.5" customHeight="1">
-      <c r="A2" s="17" t="n"/>
-      <c r="B2" s="123" t="inlineStr">
+      <c r="A2" s="320" t="n"/>
+      <c r="B2" s="315" t="inlineStr">
         <is>
           <t>Hạng mục</t>
         </is>
       </c>
-      <c r="C2" s="17" t="n"/>
-      <c r="D2" s="17" t="n"/>
-      <c r="E2" s="129" t="n"/>
-      <c r="F2" s="130" t="n"/>
-      <c r="G2" s="130" t="n"/>
-      <c r="H2" s="131" t="inlineStr">
+      <c r="C2" s="320" t="n"/>
+      <c r="D2" s="320" t="n"/>
+      <c r="E2" s="321" t="n"/>
+      <c r="F2" s="322" t="n"/>
+      <c r="G2" s="322" t="n"/>
+      <c r="H2" s="323" t="inlineStr">
         <is>
           <t>Thực đạt (Tiêu chí B,C)</t>
         </is>
       </c>
-      <c r="I2" s="131" t="inlineStr">
+      <c r="I2" s="323" t="inlineStr">
         <is>
           <t>Điểm đạt = Thực đạt/Kế hoạch (Tiêu chí B,C)</t>
         </is>
       </c>
-      <c r="J2" s="131" t="inlineStr">
+      <c r="J2" s="323" t="inlineStr">
         <is>
           <t>Tỷ lệ hoàn thành (Tiêu chí A)</t>
         </is>
       </c>
-      <c r="K2" s="132" t="inlineStr">
+      <c r="K2" s="324" t="inlineStr">
         <is>
           <t>Điểm KPIs (Tính theo công thức của tùng loại tiêu chí)</t>
         </is>
       </c>
-      <c r="L2" s="133" t="inlineStr">
+      <c r="L2" s="325" t="inlineStr">
         <is>
           <t>Thực đạt (Tiêu chí B,C)</t>
         </is>
       </c>
-      <c r="M2" s="133" t="inlineStr">
+      <c r="M2" s="325" t="inlineStr">
         <is>
           <t>Điểm đạt = Thực đạt/Kế hoạch (Tiêu chí B,C)</t>
         </is>
       </c>
-      <c r="N2" s="133" t="inlineStr">
+      <c r="N2" s="325" t="inlineStr">
         <is>
           <t>Tỷ lệ hoàn thành (Tiêu chí A)</t>
         </is>
       </c>
-      <c r="O2" s="126" t="inlineStr">
+      <c r="O2" s="318" t="inlineStr">
         <is>
           <t>Điểm KPIs (Tính theo công thức của tùng loại tiêu chí)</t>
         </is>
       </c>
-      <c r="P2" s="128" t="n"/>
-      <c r="Q2" s="128" t="n"/>
-      <c r="R2" s="128" t="n"/>
-      <c r="S2" s="128" t="n"/>
+      <c r="P2" s="319" t="n"/>
+      <c r="Q2" s="319" t="n"/>
+      <c r="R2" s="319" t="n"/>
+      <c r="S2" s="319" t="n"/>
     </row>
     <row r="3" ht="45.75" customHeight="1">
-      <c r="A3" s="134" t="inlineStr">
+      <c r="A3" s="326" t="inlineStr">
         <is>
           <t xml:space="preserve">A. </t>
         </is>
       </c>
-      <c r="B3" s="135" t="inlineStr">
-        <is>
-          <t>HIỆU QUẢ CÔNG VIỆC (TỶ TRỌNG: Max = 75%)</t>
-        </is>
-      </c>
-      <c r="C3" s="136" t="n"/>
-      <c r="D3" s="136" t="n"/>
-      <c r="E3" s="136" t="n"/>
-      <c r="F3" s="137" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> = 30% * Delivery + 20% * Quality + 10% * Reliability + 10 * Collaboration + 5% * Growth</t>
-        </is>
-      </c>
-      <c r="G3" s="136" t="n"/>
-      <c r="H3" s="138" t="n"/>
-      <c r="I3" s="138" t="n"/>
-      <c r="J3" s="138" t="n"/>
-      <c r="K3" s="139">
-        <f>(0.3*K4+0.2*K9+0.1*K15+0.1*K16+0.05*K17)/10</f>
-        <v/>
-      </c>
-      <c r="L3" s="139" t="n"/>
-      <c r="M3" s="138" t="n"/>
-      <c r="N3" s="138" t="n"/>
-      <c r="O3" s="139">
-        <f>(0.3*O4+0.2*O9+0.1*O15+0.1*O16+0.05*O17)/10</f>
-        <v/>
-      </c>
-      <c r="P3" s="128" t="n"/>
-      <c r="Q3" s="128" t="n"/>
-      <c r="R3" s="128" t="n"/>
-      <c r="S3" s="128" t="n"/>
+      <c r="B3" s="327" t="inlineStr">
+        <is>
+          <t>HIỆU QUẢ CÔNG VIỆC (TỶ TRỌNG: Max = 100%)</t>
+        </is>
+      </c>
+      <c r="C3" s="328" t="n"/>
+      <c r="D3" s="328" t="n"/>
+      <c r="E3" s="328" t="n"/>
+      <c r="F3" s="329" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> = 35% * Delivery + 20% * Quality + 5% * Reliability + 5% * Collaboration + 5% * Growth + 10% * Leadership + 20% * Impact Bonus</t>
+        </is>
+      </c>
+      <c r="G3" s="328" t="n"/>
+      <c r="H3" s="330" t="n"/>
+      <c r="I3" s="330" t="n"/>
+      <c r="J3" s="330" t="n"/>
+      <c r="K3" s="331">
+        <f>(0.35*K4+0.2*K9+0.05*K15+0.05*K16+0.05*K17+0.1*K18+0.2*K23)/10</f>
+        <v/>
+      </c>
+      <c r="L3" s="331" t="n"/>
+      <c r="M3" s="330" t="n"/>
+      <c r="N3" s="330" t="n"/>
+      <c r="O3" s="331">
+        <f>(0.35*O4+0.2*O9+0.05*O15+0.05*O16+0.05*O17+0.1*O18+0.2*O23)/10</f>
+        <v/>
+      </c>
+      <c r="P3" s="319" t="n"/>
+      <c r="Q3" s="319" t="n"/>
+      <c r="R3" s="319" t="n"/>
+      <c r="S3" s="319" t="n"/>
     </row>
     <row r="4" ht="61.5" customHeight="1">
-      <c r="A4" s="140" t="n">
+      <c r="A4" s="332" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="141" t="inlineStr">
+      <c r="B4" s="333" t="inlineStr">
         <is>
           <t>Delivery KPI</t>
         </is>
       </c>
-      <c r="C4" s="142" t="n"/>
-      <c r="D4" s="143" t="n"/>
-      <c r="E4" s="144" t="inlineStr">
+      <c r="C4" s="334" t="n"/>
+      <c r="D4" s="335" t="n"/>
+      <c r="E4" s="336" t="inlineStr">
         <is>
           <t xml:space="preserve">Tiêu chí: Delivery phản ánh khả năng chuyển giao công việc đã cam kết thành kết quả có giá trị.
 </t>
         </is>
       </c>
-      <c r="F4" s="145" t="inlineStr">
+      <c r="F4" s="337" t="inlineStr">
         <is>
           <t xml:space="preserve"> = 40% × Commitment Achievement + 25% × Schedule Performance + 20% × Work Throughput + 15% × Delivery Ownership</t>
         </is>
       </c>
-      <c r="G4" s="146" t="n"/>
-      <c r="H4" s="147" t="n"/>
-      <c r="I4" s="147" t="n"/>
-      <c r="J4" s="147" t="n"/>
-      <c r="K4" s="148">
+      <c r="G4" s="338" t="n"/>
+      <c r="H4" s="339" t="n"/>
+      <c r="I4" s="339" t="n"/>
+      <c r="J4" s="339" t="n"/>
+      <c r="K4" s="340">
         <f>0.4*K5+0.25*K6+0.2*K7+0.15*K8</f>
         <v/>
       </c>
-      <c r="L4" s="149" t="n"/>
-      <c r="M4" s="150" t="n"/>
-      <c r="N4" s="150" t="n"/>
-      <c r="O4" s="150">
+      <c r="L4" s="341" t="n"/>
+      <c r="M4" s="342" t="n"/>
+      <c r="N4" s="342" t="n"/>
+      <c r="O4" s="342">
         <f>0.4*O5+0.25*O6+0.2*O7+0.15*O8</f>
         <v/>
       </c>
-      <c r="P4" s="128" t="n"/>
-      <c r="Q4" s="128" t="n"/>
-      <c r="R4" s="128" t="n"/>
-      <c r="S4" s="128" t="n"/>
+      <c r="P4" s="319" t="n"/>
+      <c r="Q4" s="319" t="n"/>
+      <c r="R4" s="319" t="n"/>
+      <c r="S4" s="319" t="n"/>
     </row>
     <row r="5" ht="137.25" customHeight="1">
-      <c r="A5" s="151" t="n">
+      <c r="A5" s="343" t="n">
         <v>1.1</v>
       </c>
-      <c r="B5" s="152" t="inlineStr">
+      <c r="B5" s="344" t="inlineStr">
         <is>
           <t>Commitment Achievement</t>
         </is>
       </c>
-      <c r="C5" s="153" t="n"/>
-      <c r="D5" s="154" t="n"/>
-      <c r="E5" s="287" t="inlineStr">
+      <c r="C5" s="345" t="n"/>
+      <c r="D5" s="346" t="n"/>
+      <c r="E5" s="347" t="inlineStr">
         <is>
           <t>- Tiêu chí: Hoàn thành công việc đã cam kết
 - Đánh giá khả năng hoàn thành các Jira Task/Ticket đã cam kết.
@@ -6219,7 +7047,7 @@
 - Blocker ngoài khả năng kiểm soát</t>
         </is>
       </c>
-      <c r="F5" s="156" t="inlineStr">
+      <c r="F5" s="348" t="inlineStr">
         <is>
           <t xml:space="preserve">Công thức: Tỷ lệ hoàn thành -- Điểm
 ≥100%     --	100
@@ -6230,7 +7058,7 @@
 </t>
         </is>
       </c>
-      <c r="G5" s="156" t="inlineStr">
+      <c r="G5" s="348" t="inlineStr">
         <is>
           <t>Công thức: Tỷ lệ hoàn thành -- Điểm
 ≥100%     --	10
@@ -6240,55 +7068,55 @@
 &lt;80%	 -- 6.0</t>
         </is>
       </c>
-      <c r="H5" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I5" s="158" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J5" s="157" t="n">
+      <c r="H5" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I5" s="350" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J5" s="349" t="n">
         <v>1</v>
       </c>
-      <c r="K5" s="159" t="n">
+      <c r="K5" s="351" t="n">
         <v>10</v>
       </c>
-      <c r="L5" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M5" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N5" s="157" t="n">
+      <c r="L5" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M5" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N5" s="349" t="n">
         <v>0.95</v>
       </c>
-      <c r="O5" s="159" t="n">
+      <c r="O5" s="351" t="n">
         <v>9.5</v>
       </c>
-      <c r="P5" s="128" t="n"/>
-      <c r="Q5" s="128" t="n"/>
-      <c r="R5" s="128" t="n"/>
-      <c r="S5" s="128" t="n"/>
+      <c r="P5" s="319" t="n"/>
+      <c r="Q5" s="319" t="n"/>
+      <c r="R5" s="319" t="n"/>
+      <c r="S5" s="319" t="n"/>
     </row>
     <row r="6" ht="121.5" customHeight="1">
-      <c r="A6" s="151" t="n">
+      <c r="A6" s="343" t="n">
         <v>1.2</v>
       </c>
-      <c r="B6" s="152" t="inlineStr">
+      <c r="B6" s="344" t="inlineStr">
         <is>
           <t>Schedule Performance</t>
         </is>
       </c>
-      <c r="C6" s="153" t="n"/>
-      <c r="D6" s="154" t="n"/>
-      <c r="E6" s="288" t="inlineStr">
+      <c r="C6" s="345" t="n"/>
+      <c r="D6" s="346" t="n"/>
+      <c r="E6" s="352" t="inlineStr">
         <is>
           <t>-Tiêu chí: Hoàn thành đúng thời hạn
 - Đánh giá mức độ hoàn thành đúng thời hạn.
@@ -6298,7 +7126,7 @@
 - Delay do phụ thuộc team khác</t>
         </is>
       </c>
-      <c r="F6" s="156" t="inlineStr">
+      <c r="F6" s="348" t="inlineStr">
         <is>
           <t xml:space="preserve">Công thức: On-time Rate	Điểm
 ≥95%	100
@@ -6309,7 +7137,7 @@
 </t>
         </is>
       </c>
-      <c r="G6" s="156" t="inlineStr">
+      <c r="G6" s="348" t="inlineStr">
         <is>
           <t>On-time Rate --- Điểm
 ≥95%	--  10
@@ -6319,55 +7147,55 @@
 &lt;70%	 --   6.0</t>
         </is>
       </c>
-      <c r="H6" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I6" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J6" s="157" t="n">
+      <c r="H6" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I6" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J6" s="349" t="n">
         <v>1</v>
       </c>
-      <c r="K6" s="159" t="n">
+      <c r="K6" s="351" t="n">
         <v>10</v>
       </c>
-      <c r="L6" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M6" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N6" s="157" t="n">
+      <c r="L6" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M6" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N6" s="349" t="n">
         <v>0.89</v>
       </c>
-      <c r="O6" s="159" t="n">
+      <c r="O6" s="351" t="n">
         <v>8.5</v>
       </c>
-      <c r="P6" s="128" t="n"/>
-      <c r="Q6" s="128" t="n"/>
-      <c r="R6" s="128" t="n"/>
-      <c r="S6" s="128" t="n"/>
+      <c r="P6" s="319" t="n"/>
+      <c r="Q6" s="319" t="n"/>
+      <c r="R6" s="319" t="n"/>
+      <c r="S6" s="319" t="n"/>
     </row>
     <row r="7" ht="91.5" customHeight="1">
-      <c r="A7" s="151" t="n">
+      <c r="A7" s="343" t="n">
         <v>1.3</v>
       </c>
-      <c r="B7" s="152" t="inlineStr">
+      <c r="B7" s="344" t="inlineStr">
         <is>
           <t>Work Throughput</t>
         </is>
       </c>
-      <c r="C7" s="153" t="n"/>
-      <c r="D7" s="154" t="n"/>
-      <c r="E7" s="160" t="inlineStr">
+      <c r="C7" s="345" t="n"/>
+      <c r="D7" s="346" t="n"/>
+      <c r="E7" s="352" t="inlineStr">
         <is>
           <t xml:space="preserve">Tiêu chí: Khối lượng công việc hoàn thành theo Scope Score.
 Đánh giá công việc hoàn thành dựa trên level/ cấp bậc nhân sự
@@ -6377,7 +7205,7 @@
 </t>
         </is>
       </c>
-      <c r="F7" s="161" t="inlineStr">
+      <c r="F7" s="353" t="inlineStr">
         <is>
           <t>Công thức: Throughput	Điểm
 ≥95%	100
@@ -6386,7 +7214,7 @@
 &lt;80%	70</t>
         </is>
       </c>
-      <c r="G7" s="161" t="inlineStr">
+      <c r="G7" s="353" t="inlineStr">
         <is>
           <t>Throughput ---  Điểm
 ≥95%	   10
@@ -6395,62 +7223,62 @@
 &lt;80%	    7.0</t>
         </is>
       </c>
-      <c r="H7" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I7" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J7" s="162" t="n">
+      <c r="H7" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I7" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J7" s="354" t="n">
         <v>1</v>
       </c>
-      <c r="K7" s="163" t="n">
+      <c r="K7" s="355" t="n">
         <v>10</v>
       </c>
-      <c r="L7" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M7" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N7" s="157" t="n">
+      <c r="L7" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M7" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N7" s="349" t="n">
         <v>0.8</v>
       </c>
-      <c r="O7" s="159" t="n">
+      <c r="O7" s="351" t="n">
         <v>8.5</v>
       </c>
-      <c r="P7" s="128" t="n"/>
-      <c r="Q7" s="128" t="n"/>
-      <c r="R7" s="128" t="n"/>
-      <c r="S7" s="128" t="n"/>
+      <c r="P7" s="319" t="n"/>
+      <c r="Q7" s="319" t="n"/>
+      <c r="R7" s="319" t="n"/>
+      <c r="S7" s="319" t="n"/>
     </row>
     <row r="8" ht="167.25" customHeight="1">
-      <c r="A8" s="151" t="n">
+      <c r="A8" s="343" t="n">
         <v>1.4</v>
       </c>
-      <c r="B8" s="152" t="inlineStr">
+      <c r="B8" s="344" t="inlineStr">
         <is>
           <t>Delivery Ownership</t>
         </is>
       </c>
-      <c r="C8" s="153" t="n"/>
-      <c r="D8" s="154" t="n"/>
-      <c r="E8" s="164" t="inlineStr">
+      <c r="C8" s="345" t="n"/>
+      <c r="D8" s="346" t="n"/>
+      <c r="E8" s="356" t="inlineStr">
         <is>
           <t xml:space="preserve">Tiêu chí: Chủ động xử lý và đảm bảo tiến độ
 Đánh giá mức độ chủ động trong quá trình thực hiện.
 </t>
         </is>
       </c>
-      <c r="F8" s="165" t="inlineStr">
+      <c r="F8" s="357" t="inlineStr">
         <is>
           <t>Công thức: Manager đánh giá theo Rubric.
 Mức	   -    Tiêu chí
@@ -6461,7 +7289,7 @@
 1	Bị động, ảnh hưởng đến tiến độ chung</t>
         </is>
       </c>
-      <c r="G8" s="165" t="inlineStr">
+      <c r="G8" s="357" t="inlineStr">
         <is>
           <t>Mức	   -    Tiêu chí
 10 --	Luôn chủ động xử lý blocker, cảnh báo rủi ro sớm, đề xuất phương án khả thi
@@ -6471,106 +7299,106 @@
 2--	Bị động, ảnh hưởng đến tiến độ chung</t>
         </is>
       </c>
-      <c r="H8" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I8" s="166" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J8" s="167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K8" s="168" t="n">
+      <c r="H8" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I8" s="358" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J8" s="359" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K8" s="360" t="n">
         <v>10</v>
       </c>
-      <c r="L8" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M8" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N8" s="158" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O8" s="159" t="n">
+      <c r="L8" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M8" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N8" s="350" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O8" s="351" t="n">
         <v>7.5</v>
       </c>
-      <c r="P8" s="128" t="n"/>
-      <c r="Q8" s="128" t="n"/>
-      <c r="R8" s="128" t="n"/>
-      <c r="S8" s="128" t="n"/>
+      <c r="P8" s="319" t="n"/>
+      <c r="Q8" s="319" t="n"/>
+      <c r="R8" s="319" t="n"/>
+      <c r="S8" s="319" t="n"/>
     </row>
     <row r="9" ht="61.5" customHeight="1">
-      <c r="A9" s="140" t="n">
+      <c r="A9" s="332" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="169" t="inlineStr">
+      <c r="B9" s="361" t="inlineStr">
         <is>
           <t>Quality KPI</t>
         </is>
       </c>
-      <c r="C9" s="170" t="n"/>
-      <c r="D9" s="143" t="n"/>
-      <c r="E9" s="171" t="inlineStr">
+      <c r="C9" s="362" t="n"/>
+      <c r="D9" s="335" t="n"/>
+      <c r="E9" s="363" t="inlineStr">
         <is>
           <t xml:space="preserve">Tiêu chí: Quality phản ánh khả năng tạo ra phần mềm đáp ứng yêu cầu chất lượng trong toàn bộ SDLC, không chỉ là số lượng bug sau khi release.
 </t>
         </is>
       </c>
-      <c r="F9" s="172" t="inlineStr">
+      <c r="F9" s="364" t="inlineStr">
         <is>
           <t>Công thức: Quality Score = 25% × Code Quality + 20% × Testing Quality + 15% × Build &amp; Release Quality + 25% × Production Quality + 15% × Quality Process Compliance</t>
         </is>
       </c>
-      <c r="G9" s="173" t="n"/>
-      <c r="H9" s="147" t="n"/>
-      <c r="I9" s="147" t="n"/>
-      <c r="J9" s="174" t="n"/>
-      <c r="K9" s="175">
+      <c r="G9" s="365" t="n"/>
+      <c r="H9" s="339" t="n"/>
+      <c r="I9" s="339" t="n"/>
+      <c r="J9" s="366" t="n"/>
+      <c r="K9" s="367">
         <f>0.25*K10+0.2*K11+0.15*K12+0.25*K13+0.15*K14</f>
         <v/>
       </c>
-      <c r="L9" s="176" t="n"/>
-      <c r="M9" s="150" t="n"/>
-      <c r="N9" s="150" t="n"/>
-      <c r="O9" s="150">
+      <c r="L9" s="368" t="n"/>
+      <c r="M9" s="342" t="n"/>
+      <c r="N9" s="342" t="n"/>
+      <c r="O9" s="342">
         <f>0.25*O10+0.2*O11+0.15*O12+0.25*O13+0.15*O14</f>
         <v/>
       </c>
-      <c r="P9" s="128" t="n"/>
-      <c r="Q9" s="128" t="n"/>
-      <c r="R9" s="128" t="n"/>
-      <c r="S9" s="128" t="n"/>
+      <c r="P9" s="319" t="n"/>
+      <c r="Q9" s="319" t="n"/>
+      <c r="R9" s="319" t="n"/>
+      <c r="S9" s="319" t="n"/>
     </row>
     <row r="10" ht="107.25" customHeight="1">
-      <c r="A10" s="151" t="n">
+      <c r="A10" s="343" t="n">
         <v>2.1</v>
       </c>
-      <c r="B10" s="177" t="inlineStr">
+      <c r="B10" s="369" t="inlineStr">
         <is>
           <t>Code Quality</t>
         </is>
       </c>
-      <c r="C10" s="178" t="n"/>
-      <c r="D10" s="154" t="n"/>
-      <c r="E10" s="179" t="inlineStr">
+      <c r="C10" s="370" t="n"/>
+      <c r="D10" s="346" t="n"/>
+      <c r="E10" s="371" t="inlineStr">
         <is>
           <t>Đánh giá chất lượng mã nguồn trước khi merge.</t>
         </is>
       </c>
-      <c r="F10" s="161" t="inlineStr">
+      <c r="F10" s="353" t="inlineStr">
         <is>
           <t xml:space="preserve">Điểm    ---    Đánh giá
 95–100	Xuất sắc
@@ -6581,7 +7409,7 @@
 </t>
         </is>
       </c>
-      <c r="G10" s="156" t="inlineStr">
+      <c r="G10" s="348" t="inlineStr">
         <is>
           <t xml:space="preserve">Điểm    ---    Đánh giá
 9.5–10	Xuất sắc
@@ -6592,59 +7420,59 @@
 </t>
         </is>
       </c>
-      <c r="H10" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I10" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J10" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K10" s="180" t="n">
+      <c r="H10" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I10" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J10" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K10" s="372" t="n">
         <v>10</v>
       </c>
-      <c r="L10" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M10" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N10" s="159" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O10" s="180" t="n">
+      <c r="L10" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M10" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N10" s="351" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O10" s="372" t="n">
         <v>8.5</v>
       </c>
-      <c r="P10" s="128" t="n"/>
-      <c r="Q10" s="128" t="n"/>
-      <c r="R10" s="128" t="n"/>
-      <c r="S10" s="128" t="n"/>
+      <c r="P10" s="319" t="n"/>
+      <c r="Q10" s="319" t="n"/>
+      <c r="R10" s="319" t="n"/>
+      <c r="S10" s="319" t="n"/>
     </row>
     <row r="11" ht="107.25" customHeight="1">
-      <c r="A11" s="151" t="n">
+      <c r="A11" s="343" t="n">
         <v>2.2</v>
       </c>
-      <c r="B11" s="177" t="inlineStr">
+      <c r="B11" s="369" t="inlineStr">
         <is>
           <t>Testing Quality</t>
         </is>
       </c>
-      <c r="C11" s="178" t="n"/>
-      <c r="D11" s="154" t="n"/>
-      <c r="E11" s="181" t="inlineStr">
+      <c r="C11" s="370" t="n"/>
+      <c r="D11" s="346" t="n"/>
+      <c r="E11" s="373" t="inlineStr">
         <is>
           <t>Đánh giá chất lượng kiểm thử (self test)
 Tham số đầu vào:
@@ -6655,61 +7483,61 @@
 - Flaky Test</t>
         </is>
       </c>
-      <c r="F11" s="182" t="n"/>
-      <c r="G11" s="182" t="n"/>
-      <c r="H11" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I11" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J11" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K11" s="180" t="n">
+      <c r="F11" s="374" t="n"/>
+      <c r="G11" s="374" t="n"/>
+      <c r="H11" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I11" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J11" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K11" s="372" t="n">
         <v>10</v>
       </c>
-      <c r="L11" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M11" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N11" s="159" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O11" s="180" t="n">
+      <c r="L11" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M11" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N11" s="351" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O11" s="372" t="n">
         <v>9</v>
       </c>
-      <c r="P11" s="128" t="n"/>
-      <c r="Q11" s="128" t="n"/>
-      <c r="R11" s="128" t="n"/>
-      <c r="S11" s="128" t="n"/>
+      <c r="P11" s="319" t="n"/>
+      <c r="Q11" s="319" t="n"/>
+      <c r="R11" s="319" t="n"/>
+      <c r="S11" s="319" t="n"/>
     </row>
     <row r="12" ht="91.5" customHeight="1">
-      <c r="A12" s="151" t="n">
+      <c r="A12" s="343" t="n">
         <v>2.3</v>
       </c>
-      <c r="B12" s="177" t="inlineStr">
+      <c r="B12" s="369" t="inlineStr">
         <is>
           <t xml:space="preserve">Build &amp; Release Quality </t>
         </is>
       </c>
-      <c r="C12" s="178" t="n"/>
-      <c r="D12" s="154" t="n"/>
-      <c r="E12" s="183" t="inlineStr">
+      <c r="C12" s="370" t="n"/>
+      <c r="D12" s="346" t="n"/>
+      <c r="E12" s="375" t="inlineStr">
         <is>
           <t>Đánh giá chất lượng build.
 Tham số:
@@ -6719,7 +7547,7 @@
 - Release Checklist</t>
         </is>
       </c>
-      <c r="F12" s="156" t="inlineStr">
+      <c r="F12" s="348" t="inlineStr">
         <is>
           <t xml:space="preserve">Điều kiện  ---	Điểm
 Không lỗi build, không rollback	100
@@ -6729,7 +7557,7 @@
 </t>
         </is>
       </c>
-      <c r="G12" s="156" t="inlineStr">
+      <c r="G12" s="348" t="inlineStr">
         <is>
           <t>Điều kiện  ---	Điểm
 Không lỗi build, không rollback	-- 10
@@ -6738,59 +7566,59 @@
 Rollback Production  ---  6.0</t>
         </is>
       </c>
-      <c r="H12" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I12" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J12" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K12" s="180" t="n">
+      <c r="H12" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I12" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J12" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K12" s="372" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M12" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N12" s="159" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O12" s="180" t="n">
+      <c r="L12" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M12" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N12" s="351" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O12" s="372" t="n">
         <v>9.5</v>
       </c>
-      <c r="P12" s="128" t="n"/>
-      <c r="Q12" s="128" t="n"/>
-      <c r="R12" s="128" t="n"/>
-      <c r="S12" s="128" t="n"/>
+      <c r="P12" s="319" t="n"/>
+      <c r="Q12" s="319" t="n"/>
+      <c r="R12" s="319" t="n"/>
+      <c r="S12" s="319" t="n"/>
     </row>
     <row r="13" ht="107.25" customHeight="1">
-      <c r="A13" s="151" t="n">
+      <c r="A13" s="343" t="n">
         <v>2.4</v>
       </c>
-      <c r="B13" s="177" t="inlineStr">
+      <c r="B13" s="369" t="inlineStr">
         <is>
           <t>Production Quality</t>
         </is>
       </c>
-      <c r="C13" s="178" t="n"/>
-      <c r="D13" s="154" t="n"/>
-      <c r="E13" s="183" t="inlineStr">
+      <c r="C13" s="370" t="n"/>
+      <c r="D13" s="346" t="n"/>
+      <c r="E13" s="375" t="inlineStr">
         <is>
           <t>Đây là nhóm phản ánh Outcome của Quality.
 Tham số:
@@ -6800,7 +7628,7 @@
 - Customer Complaint</t>
         </is>
       </c>
-      <c r="F13" s="161" t="inlineStr">
+      <c r="F13" s="353" t="inlineStr">
         <is>
           <t xml:space="preserve">Điều kiện	Điểm
 Không Critical Bug	100
@@ -6811,7 +7639,7 @@
 </t>
         </is>
       </c>
-      <c r="G13" s="161" t="inlineStr">
+      <c r="G13" s="353" t="inlineStr">
         <is>
           <t xml:space="preserve">Điều kiện ---	Điểm
 Không Critical Bug ---	10
@@ -6822,59 +7650,59 @@
 </t>
         </is>
       </c>
-      <c r="H13" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I13" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J13" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K13" s="180" t="n">
+      <c r="H13" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I13" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J13" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K13" s="372" t="n">
         <v>10</v>
       </c>
-      <c r="L13" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M13" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N13" s="159" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O13" s="180" t="n">
+      <c r="L13" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M13" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N13" s="351" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O13" s="372" t="n">
         <v>9</v>
       </c>
-      <c r="P13" s="128" t="n"/>
-      <c r="Q13" s="128" t="n"/>
-      <c r="R13" s="128" t="n"/>
-      <c r="S13" s="128" t="n"/>
+      <c r="P13" s="319" t="n"/>
+      <c r="Q13" s="319" t="n"/>
+      <c r="R13" s="319" t="n"/>
+      <c r="S13" s="319" t="n"/>
     </row>
     <row r="14" ht="121.5" customHeight="1">
-      <c r="A14" s="151" t="n">
+      <c r="A14" s="343" t="n">
         <v>2.5</v>
       </c>
-      <c r="B14" s="177" t="inlineStr">
+      <c r="B14" s="369" t="inlineStr">
         <is>
           <t>Quality Process Compliance</t>
         </is>
       </c>
-      <c r="C14" s="178" t="n"/>
-      <c r="D14" s="154" t="n"/>
-      <c r="E14" s="183" t="inlineStr">
+      <c r="C14" s="370" t="n"/>
+      <c r="D14" s="346" t="n"/>
+      <c r="E14" s="375" t="inlineStr">
         <is>
           <t>Đánh giá việc tuân thủ Quality Practice.
 Tham số: 
@@ -6885,7 +7713,7 @@
 - Documentation</t>
         </is>
       </c>
-      <c r="F14" s="165" t="inlineStr">
+      <c r="F14" s="357" t="inlineStr">
         <is>
           <t xml:space="preserve">Mức	Mô tả
 5	Luôn tuân thủ đầy đủ quy trình
@@ -6896,7 +7724,7 @@
 </t>
         </is>
       </c>
-      <c r="G14" s="165" t="inlineStr">
+      <c r="G14" s="357" t="inlineStr">
         <is>
           <t xml:space="preserve">Mức   ---	Mô tả
 10	Luôn tuân thủ đầy đủ quy trình
@@ -6907,59 +7735,59 @@
 </t>
         </is>
       </c>
-      <c r="H14" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I14" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J14" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K14" s="180" t="n">
+      <c r="H14" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I14" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J14" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K14" s="372" t="n">
         <v>10</v>
       </c>
-      <c r="L14" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M14" s="157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N14" s="159" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O14" s="184" t="n">
+      <c r="L14" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M14" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N14" s="351" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O14" s="376" t="n">
         <v>9</v>
       </c>
-      <c r="P14" s="128" t="n"/>
-      <c r="Q14" s="128" t="n"/>
-      <c r="R14" s="128" t="n"/>
-      <c r="S14" s="128" t="n"/>
+      <c r="P14" s="319" t="n"/>
+      <c r="Q14" s="319" t="n"/>
+      <c r="R14" s="319" t="n"/>
+      <c r="S14" s="319" t="n"/>
     </row>
     <row r="15" ht="121.5" customHeight="1">
-      <c r="A15" s="140" t="n">
+      <c r="A15" s="332" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="169" t="inlineStr">
+      <c r="B15" s="361" t="inlineStr">
         <is>
           <t>Reliability KPI</t>
         </is>
       </c>
-      <c r="C15" s="185" t="n"/>
-      <c r="D15" s="186" t="n"/>
-      <c r="E15" s="144" t="inlineStr">
+      <c r="C15" s="377" t="n"/>
+      <c r="D15" s="378" t="n"/>
+      <c r="E15" s="336" t="inlineStr">
         <is>
           <t>Reliability phản ánh khả năng đảm bảo hệ thống vận hành ổn định sau khi thay đổi.
 Collaboration đánh giá:
@@ -6970,45 +7798,45 @@
 - Khả năng tạo ảnh hưởng tích cực</t>
         </is>
       </c>
-      <c r="F15" s="187" t="inlineStr">
+      <c r="F15" s="379" t="inlineStr">
         <is>
           <t>Cá nhân + Manager đánh giá</t>
         </is>
       </c>
-      <c r="G15" s="188" t="n"/>
-      <c r="H15" s="189" t="n"/>
-      <c r="I15" s="189" t="n"/>
-      <c r="J15" s="189" t="n">
+      <c r="G15" s="380" t="n"/>
+      <c r="H15" s="381" t="n"/>
+      <c r="I15" s="381" t="n"/>
+      <c r="J15" s="381" t="n">
         <v>1</v>
       </c>
-      <c r="K15" s="190" t="n">
+      <c r="K15" s="382" t="n">
         <v>10</v>
       </c>
-      <c r="L15" s="190" t="n"/>
-      <c r="M15" s="189" t="n"/>
-      <c r="N15" s="189" t="n">
+      <c r="L15" s="382" t="n"/>
+      <c r="M15" s="381" t="n"/>
+      <c r="N15" s="381" t="n">
         <v>0.95</v>
       </c>
-      <c r="O15" s="186" t="n">
+      <c r="O15" s="378" t="n">
         <v>9.5</v>
       </c>
-      <c r="P15" s="128" t="n"/>
-      <c r="Q15" s="128" t="n"/>
-      <c r="R15" s="128" t="n"/>
-      <c r="S15" s="128" t="n"/>
+      <c r="P15" s="319" t="n"/>
+      <c r="Q15" s="319" t="n"/>
+      <c r="R15" s="319" t="n"/>
+      <c r="S15" s="319" t="n"/>
     </row>
     <row r="16" ht="121.5" customHeight="1">
-      <c r="A16" s="140" t="n">
+      <c r="A16" s="332" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="169" t="inlineStr">
+      <c r="B16" s="361" t="inlineStr">
         <is>
           <t>Collaboration KPI</t>
         </is>
       </c>
-      <c r="C16" s="185" t="n"/>
-      <c r="D16" s="186" t="n"/>
-      <c r="E16" s="144" t="inlineStr">
+      <c r="C16" s="377" t="n"/>
+      <c r="D16" s="378" t="n"/>
+      <c r="E16" s="336" t="inlineStr">
         <is>
           <t>Collaboration phản ánh khả năng phối hợp để nâng cao hiệu quả của Team, không phải khả năng giao tiếp đơn thuần.
 Collaboration đánh giá:
@@ -7019,45 +7847,45 @@
 - Khả năng tạo ảnh hưởng tích cực</t>
         </is>
       </c>
-      <c r="F16" s="187" t="inlineStr">
+      <c r="F16" s="379" t="inlineStr">
         <is>
           <t>Tự đánh giá</t>
         </is>
       </c>
-      <c r="G16" s="188" t="n"/>
-      <c r="H16" s="189" t="n"/>
-      <c r="I16" s="189" t="n"/>
-      <c r="J16" s="189" t="n">
+      <c r="G16" s="380" t="n"/>
+      <c r="H16" s="381" t="n"/>
+      <c r="I16" s="381" t="n"/>
+      <c r="J16" s="381" t="n">
         <v>1</v>
       </c>
-      <c r="K16" s="190" t="n">
+      <c r="K16" s="382" t="n">
         <v>10</v>
       </c>
-      <c r="L16" s="190" t="n"/>
-      <c r="M16" s="189" t="n"/>
-      <c r="N16" s="189" t="n">
+      <c r="L16" s="382" t="n"/>
+      <c r="M16" s="381" t="n"/>
+      <c r="N16" s="381" t="n">
         <v>0.9</v>
       </c>
-      <c r="O16" s="186" t="n">
+      <c r="O16" s="378" t="n">
         <v>9</v>
       </c>
-      <c r="P16" s="128" t="n"/>
-      <c r="Q16" s="128" t="n"/>
-      <c r="R16" s="128" t="n"/>
-      <c r="S16" s="128" t="n"/>
+      <c r="P16" s="319" t="n"/>
+      <c r="Q16" s="319" t="n"/>
+      <c r="R16" s="319" t="n"/>
+      <c r="S16" s="319" t="n"/>
     </row>
     <row r="17" ht="183" customHeight="1">
-      <c r="A17" s="140" t="n">
+      <c r="A17" s="332" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="169" t="inlineStr">
+      <c r="B17" s="361" t="inlineStr">
         <is>
           <t>Growth KPI</t>
         </is>
       </c>
-      <c r="C17" s="185" t="n"/>
-      <c r="D17" s="186" t="n"/>
-      <c r="E17" s="191" t="inlineStr">
+      <c r="C17" s="377" t="n"/>
+      <c r="D17" s="378" t="n"/>
+      <c r="E17" s="383" t="inlineStr">
         <is>
           <t>Growth phản ánh sự phát triển năng lực của cá nhân và khả năng đóng góp vào sự phát triển năng lực của tổ chức.
 Growth không đánh giá:
@@ -7071,597 +7899,2867 @@
 - Khả năng phát triển người khác</t>
         </is>
       </c>
-      <c r="F17" s="192" t="inlineStr">
+      <c r="F17" s="384" t="inlineStr">
         <is>
           <t>Tự đánh giá</t>
         </is>
       </c>
-      <c r="G17" s="193" t="n"/>
-      <c r="H17" s="194" t="n"/>
-      <c r="I17" s="194" t="n"/>
-      <c r="J17" s="194" t="n">
+      <c r="G17" s="385" t="n"/>
+      <c r="H17" s="386" t="n"/>
+      <c r="I17" s="386" t="n"/>
+      <c r="J17" s="386" t="n">
         <v>1</v>
       </c>
-      <c r="K17" s="195" t="n">
+      <c r="K17" s="387" t="n">
         <v>10</v>
       </c>
-      <c r="L17" s="195" t="n"/>
-      <c r="M17" s="189" t="n"/>
-      <c r="N17" s="189" t="n">
+      <c r="L17" s="387" t="n"/>
+      <c r="M17" s="381" t="n"/>
+      <c r="N17" s="381" t="n">
         <v>0.8</v>
       </c>
-      <c r="O17" s="186" t="n">
+      <c r="O17" s="378" t="n">
         <v>8</v>
       </c>
-      <c r="P17" s="128" t="n"/>
-      <c r="Q17" s="128" t="n"/>
-      <c r="R17" s="128" t="n"/>
-      <c r="S17" s="128" t="n"/>
-    </row>
-    <row r="18" ht="30.75" customHeight="1">
-      <c r="A18" s="196" t="inlineStr">
+      <c r="P17" s="319" t="n"/>
+      <c r="Q17" s="319" t="n"/>
+      <c r="R17" s="319" t="n"/>
+      <c r="S17" s="319" t="n"/>
+    </row>
+    <row r="18" ht="61.5" customHeight="1">
+      <c r="A18" s="332" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" s="361" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="C18" s="377" t="n"/>
+      <c r="D18" s="382" t="n"/>
+      <c r="E18" s="466" t="inlineStr">
+        <is>
+          <t>Đánh giá khả năng lãnh đạo kỹ thuật và phát triển đội ngũ</t>
+        </is>
+      </c>
+      <c r="F18" s="383" t="inlineStr">
+        <is>
+          <t>Công thức: 30% * Team Delivery Management + 30% *People Leadership + 20% * Team Operation +18:1820% * Engineering Governace</t>
+        </is>
+      </c>
+      <c r="G18" s="385" t="n"/>
+      <c r="H18" s="386" t="n"/>
+      <c r="I18" s="386" t="n"/>
+      <c r="J18" s="386" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K18" s="387" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="387" t="n"/>
+      <c r="M18" s="381" t="n"/>
+      <c r="N18" s="381" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O18" s="378" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="319" t="n"/>
+      <c r="Q18" s="319" t="n"/>
+      <c r="R18" s="319" t="n"/>
+      <c r="S18" s="319" t="n"/>
+    </row>
+    <row r="19" ht="91.5" customHeight="1">
+      <c r="A19" s="343" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="B19" s="369" t="inlineStr">
+        <is>
+          <t>Team Delivery Management</t>
+        </is>
+      </c>
+      <c r="C19" s="370" t="n"/>
+      <c r="D19" s="346" t="n"/>
+      <c r="E19" s="467" t="inlineStr">
+        <is>
+          <t>Đo khả năng giúp team hoàn thành công việc.
+Đánh giá dựa trên:
+- Planning
+- Risk management
+- Workload balancing
+- Blocker removal</t>
+        </is>
+      </c>
+      <c r="F19" s="357" t="inlineStr">
+        <is>
+          <t>Tự đánh giá</t>
+        </is>
+      </c>
+      <c r="G19" s="357" t="n"/>
+      <c r="H19" s="349" t="n"/>
+      <c r="I19" s="349" t="n"/>
+      <c r="J19" s="349" t="n"/>
+      <c r="K19" s="372" t="n"/>
+      <c r="L19" s="349" t="n"/>
+      <c r="M19" s="349" t="n"/>
+      <c r="N19" s="351" t="n"/>
+      <c r="O19" s="376" t="n"/>
+      <c r="P19" s="319" t="n"/>
+      <c r="Q19" s="319" t="n"/>
+      <c r="R19" s="319" t="n"/>
+      <c r="S19" s="319" t="n"/>
+    </row>
+    <row r="20" ht="76.5" customHeight="1">
+      <c r="A20" s="343" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="B20" s="369" t="inlineStr">
+        <is>
+          <t>Đo khả năng phát triển con người.</t>
+        </is>
+      </c>
+      <c r="C20" s="370" t="n"/>
+      <c r="D20" s="346" t="n"/>
+      <c r="E20" s="375" t="inlineStr">
+        <is>
+          <t>- mentoring
+- coaching
+- onboarding
+- technical guidance
+- phát triển Junior</t>
+        </is>
+      </c>
+      <c r="F20" s="357" t="inlineStr">
+        <is>
+          <t>Tự đánh giá</t>
+        </is>
+      </c>
+      <c r="G20" s="357" t="n"/>
+      <c r="H20" s="349" t="n"/>
+      <c r="I20" s="349" t="n"/>
+      <c r="J20" s="349" t="n"/>
+      <c r="K20" s="372" t="n"/>
+      <c r="L20" s="349" t="n"/>
+      <c r="M20" s="349" t="n"/>
+      <c r="N20" s="351" t="n"/>
+      <c r="O20" s="376" t="n"/>
+      <c r="P20" s="319" t="n"/>
+      <c r="Q20" s="319" t="n"/>
+      <c r="R20" s="319" t="n"/>
+      <c r="S20" s="319" t="n"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="343" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="B21" s="369" t="inlineStr">
+        <is>
+          <t>Team Operation</t>
+        </is>
+      </c>
+      <c r="C21" s="370" t="n"/>
+      <c r="D21" s="346" t="n"/>
+      <c r="E21" s="375" t="inlineStr">
+        <is>
+          <t>Quản lý hoạt động của team theo qui trình</t>
+        </is>
+      </c>
+      <c r="F21" s="357" t="inlineStr">
+        <is>
+          <t>Tự đánh giá</t>
+        </is>
+      </c>
+      <c r="G21" s="357" t="n"/>
+      <c r="H21" s="349" t="n"/>
+      <c r="I21" s="349" t="n"/>
+      <c r="J21" s="349" t="n"/>
+      <c r="K21" s="372" t="n"/>
+      <c r="L21" s="349" t="n"/>
+      <c r="M21" s="349" t="n"/>
+      <c r="N21" s="351" t="n"/>
+      <c r="O21" s="376" t="n"/>
+      <c r="P21" s="319" t="n"/>
+      <c r="Q21" s="319" t="n"/>
+      <c r="R21" s="319" t="n"/>
+      <c r="S21" s="319" t="n"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="343" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="B22" s="369" t="inlineStr">
+        <is>
+          <t>Engineering Governance</t>
+        </is>
+      </c>
+      <c r="C22" s="370" t="n"/>
+      <c r="D22" s="346" t="n"/>
+      <c r="E22" s="375" t="inlineStr">
+        <is>
+          <t>Duy trì chuẩn kỹ thuật</t>
+        </is>
+      </c>
+      <c r="F22" s="357" t="inlineStr">
+        <is>
+          <t>Tự đánh giá</t>
+        </is>
+      </c>
+      <c r="G22" s="357" t="n"/>
+      <c r="H22" s="349" t="n"/>
+      <c r="I22" s="349" t="n"/>
+      <c r="J22" s="349" t="n"/>
+      <c r="K22" s="372" t="n"/>
+      <c r="L22" s="349" t="n"/>
+      <c r="M22" s="349" t="n"/>
+      <c r="N22" s="351" t="n"/>
+      <c r="O22" s="376" t="n"/>
+      <c r="P22" s="319" t="n"/>
+      <c r="Q22" s="319" t="n"/>
+      <c r="R22" s="319" t="n"/>
+      <c r="S22" s="319" t="n"/>
+    </row>
+    <row r="23" ht="290.25" customHeight="1">
+      <c r="A23" s="332" t="n">
+        <v>7</v>
+      </c>
+      <c r="B23" s="361" t="inlineStr">
+        <is>
+          <t>Impact Bonus</t>
+        </is>
+      </c>
+      <c r="C23" s="377" t="n"/>
+      <c r="D23" s="378" t="n"/>
+      <c r="E23" s="383" t="inlineStr">
+        <is>
+          <t>Ghi nhận các giá trị phát sinh ngoài kế hoạch. 
+Ví dụ cho dev:
+- phát hiện bug nghiêm trọng trước khi release
+- nghĩ ra giải pháp giúp giảm 70% thời gian build
+- cứu production lúc nửa đêm
+- viết framework dùng chung cho toàn công ty
+Để tránh cảm tính, mỗi đóng góp nên đáp ứng đủ các tiêu chí:
+- Không nằm trong kế hoạch KPI ban đầu.
+- Có bằng chứng rõ ràng (PR, RFC, tài liệu, RCA, dashboard, số liệu...).
+- Được quản lý hoặc hội đồng xác nhận.
+- Tạo ra giá trị đo được hoặc tác động rõ ràng.</t>
+        </is>
+      </c>
+      <c r="F23" s="388" t="inlineStr">
+        <is>
+          <t>Công thức:
+- 0%: Không có đóng góp
+- 25%: Đóng góp tạo giá trị cho bản thân hoặc một hạng mục nhỏ. Ví dụ: automation cá nhân, phát hiện bug quan trọng, cải tiến workflow cá nhân.
+- 50%: Đóng góp mang lại lợi ích cho cả team. Ví dụ: xây reusable component, tối ưu CI/CD của team, cải thiện coding guideline, mentoring hiệu quả.
+- 75%: Đóng góp được nhiều team sử dụng hoặc tạo ảnh hưởng liên phòng ban. Ví dụ: xây internal library, framework dùng chung, xử lý production incident lớn, đào tạo nhiều team.
+- 100%: Đóng góp tạo ảnh hưởng rõ rệt tới toàn bộ Engineering hoặc doanh nghiệp. Ví dụ: nền tảng mới giúp giảm đáng kể chi phí/vận hành, sáng kiến được triển khai toàn công ty, giải pháp tạo lợi thế cạnh tranh hoặc doanh thu.</t>
+        </is>
+      </c>
+      <c r="G23" s="385" t="n"/>
+      <c r="H23" s="386" t="n"/>
+      <c r="I23" s="386" t="n"/>
+      <c r="J23" s="386" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K23" s="387" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="387" t="n"/>
+      <c r="M23" s="381" t="n"/>
+      <c r="N23" s="381" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O23" s="378" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="319" t="n"/>
+      <c r="Q23" s="319" t="n"/>
+      <c r="R23" s="319" t="n"/>
+      <c r="S23" s="319" t="n"/>
+    </row>
+    <row r="24" ht="30.75" customHeight="1">
+      <c r="A24" s="343" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="B24" s="369" t="inlineStr">
+        <is>
+          <t>Innovation (tạo ra giá trị mới)</t>
+        </is>
+      </c>
+      <c r="C24" s="370" t="n"/>
+      <c r="D24" s="346" t="n"/>
+      <c r="E24" s="375" t="inlineStr">
+        <is>
+          <t>Tạo ra giá trị mới cho công ty.
+Ví dụ: Viết script giúp giảm 6 giờ release xuống còn 20 phút.</t>
+        </is>
+      </c>
+      <c r="F24" s="389" t="n"/>
+      <c r="G24" s="389" t="n"/>
+      <c r="H24" s="349" t="n"/>
+      <c r="I24" s="349" t="n"/>
+      <c r="J24" s="349" t="n"/>
+      <c r="K24" s="372" t="n"/>
+      <c r="L24" s="349" t="n"/>
+      <c r="M24" s="349" t="n"/>
+      <c r="N24" s="351" t="n"/>
+      <c r="O24" s="376" t="n"/>
+      <c r="P24" s="319" t="n"/>
+      <c r="Q24" s="319" t="n"/>
+      <c r="R24" s="319" t="n"/>
+      <c r="S24" s="319" t="n"/>
+    </row>
+    <row r="25" ht="76.5" customHeight="1">
+      <c r="A25" s="343" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="B25" s="369" t="inlineStr">
+        <is>
+          <t>Exceptional Contribution</t>
+        </is>
+      </c>
+      <c r="C25" s="370" t="n"/>
+      <c r="D25" s="346" t="n"/>
+      <c r="E25" s="375" t="inlineStr">
+        <is>
+          <t>Làm vượt kỳ vọng.
+Ví dụ:
+- hoàn thành dự án trước deadline lớn
+- hỗ trợ nhiều team
+- xử lý workload đột biến</t>
+        </is>
+      </c>
+      <c r="F25" s="390" t="n"/>
+      <c r="G25" s="390" t="n"/>
+      <c r="H25" s="349" t="n"/>
+      <c r="I25" s="349" t="n"/>
+      <c r="J25" s="349" t="n"/>
+      <c r="K25" s="372" t="n"/>
+      <c r="L25" s="349" t="n"/>
+      <c r="M25" s="349" t="n"/>
+      <c r="N25" s="351" t="n"/>
+      <c r="O25" s="376" t="n"/>
+      <c r="P25" s="319" t="n"/>
+      <c r="Q25" s="319" t="n"/>
+      <c r="R25" s="319" t="n"/>
+      <c r="S25" s="319" t="n"/>
+    </row>
+    <row r="26" ht="91.5" customHeight="1">
+      <c r="A26" s="343" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="B26" s="369" t="inlineStr">
+        <is>
+          <t>Organization Impact</t>
+        </is>
+      </c>
+      <c r="C26" s="370" t="n"/>
+      <c r="D26" s="346" t="n"/>
+      <c r="E26" s="375" t="inlineStr">
+        <is>
+          <t>Ảnh hưởng ở cấp tổ chức.
+Ví dụ: 
+- xây Coding Standard
+- tạo Handbook
+- đào tạo nội bộ (workshop)
+- mentoring nhiều team</t>
+        </is>
+      </c>
+      <c r="F26" s="390" t="n"/>
+      <c r="G26" s="390" t="n"/>
+      <c r="H26" s="349" t="n"/>
+      <c r="I26" s="349" t="n"/>
+      <c r="J26" s="349" t="n"/>
+      <c r="K26" s="372" t="n"/>
+      <c r="L26" s="349" t="n"/>
+      <c r="M26" s="349" t="n"/>
+      <c r="N26" s="351" t="n"/>
+      <c r="O26" s="376" t="n"/>
+      <c r="P26" s="319" t="n"/>
+      <c r="Q26" s="319" t="n"/>
+      <c r="R26" s="319" t="n"/>
+      <c r="S26" s="319" t="n"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="343" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="B27" s="369" t="inlineStr">
+        <is>
+          <t>Emergency Response</t>
+        </is>
+      </c>
+      <c r="C27" s="370" t="n"/>
+      <c r="D27" s="346" t="n"/>
+      <c r="E27" s="375" t="inlineStr">
+        <is>
+          <t>Xử lý tình huống khẩn cấp ảnh hưởng tới công ty / tổ chức</t>
+        </is>
+      </c>
+      <c r="F27" s="29" t="n"/>
+      <c r="G27" s="29" t="n"/>
+      <c r="H27" s="349" t="n"/>
+      <c r="I27" s="349" t="n"/>
+      <c r="J27" s="349" t="n"/>
+      <c r="K27" s="372" t="n"/>
+      <c r="L27" s="349" t="n"/>
+      <c r="M27" s="349" t="n"/>
+      <c r="N27" s="351" t="n"/>
+      <c r="O27" s="376" t="n"/>
+      <c r="P27" s="319" t="n"/>
+      <c r="Q27" s="319" t="n"/>
+      <c r="R27" s="319" t="n"/>
+      <c r="S27" s="319" t="n"/>
+    </row>
+    <row r="28" ht="30.75" customHeight="1">
+      <c r="A28" s="391" t="inlineStr">
         <is>
           <t>B.</t>
         </is>
       </c>
-      <c r="B18" s="197" t="inlineStr">
-        <is>
-          <t>TINH THẦN VÀ TRÁCH NHIỆM (TỶ TRỌNG: 20%)</t>
-        </is>
-      </c>
-      <c r="C18" s="198" t="n"/>
-      <c r="D18" s="199">
-        <f>SUBTOTAL(9,D19:D21)</f>
-        <v/>
-      </c>
-      <c r="E18" s="200" t="n"/>
-      <c r="F18" s="285" t="inlineStr">
-        <is>
-          <t>= Trọng số * Điểm đạt * Tỷ trọng</t>
-        </is>
-      </c>
-      <c r="G18" s="201" t="n"/>
-      <c r="H18" s="202" t="n"/>
-      <c r="I18" s="202" t="n"/>
-      <c r="J18" s="202" t="n"/>
-      <c r="K18" s="311">
-        <f>SUBTOTAL(9,K19:K21)</f>
-        <v/>
-      </c>
-      <c r="L18" s="312" t="n"/>
-      <c r="M18" s="205" t="n"/>
-      <c r="N18" s="206" t="n"/>
-      <c r="O18" s="299">
-        <f>SUBTOTAL(9,O19:O21)</f>
-        <v/>
-      </c>
-      <c r="P18" s="208" t="n"/>
-      <c r="Q18" s="209" t="n"/>
-      <c r="R18" s="210" t="n"/>
-      <c r="S18" s="211" t="n"/>
-      <c r="T18" s="211" t="n"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="212" t="n">
+      <c r="B28" s="392" t="inlineStr">
+        <is>
+          <t>TINH THẦN VÀ TRÁCH NHIỆM (TỶ TRỌNG: 15%)</t>
+        </is>
+      </c>
+      <c r="C28" s="393" t="n"/>
+      <c r="D28" s="394">
+        <f>SUBTOTAL(9,D29:D31)</f>
+        <v/>
+      </c>
+      <c r="E28" s="395" t="n"/>
+      <c r="F28" s="395">
+        <f> Trọng số * Điểm đạt * Tỷ trọng</f>
+        <v/>
+      </c>
+      <c r="G28" s="396" t="n"/>
+      <c r="H28" s="397" t="n"/>
+      <c r="I28" s="397" t="n"/>
+      <c r="J28" s="397" t="n"/>
+      <c r="K28" s="398">
+        <f>SUBTOTAL(9,K29:K31)</f>
+        <v/>
+      </c>
+      <c r="L28" s="399" t="n"/>
+      <c r="M28" s="400" t="n"/>
+      <c r="N28" s="401" t="n"/>
+      <c r="O28" s="402">
+        <f>SUBTOTAL(9,O29:O31)</f>
+        <v/>
+      </c>
+      <c r="P28" s="403" t="n"/>
+      <c r="Q28" s="404" t="n"/>
+      <c r="R28" s="405" t="n"/>
+      <c r="S28" s="406" t="n"/>
+      <c r="T28" s="406" t="n"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="407" t="n">
         <v>1</v>
       </c>
-      <c r="B19" s="213" t="inlineStr">
+      <c r="B29" s="408" t="inlineStr">
         <is>
           <t>Chủ động trong công việc</t>
         </is>
       </c>
-      <c r="C19" s="167" t="n">
+      <c r="C29" s="359" t="n">
         <v>10</v>
       </c>
-      <c r="D19" s="214" t="n">
+      <c r="D29" s="409" t="n">
         <v>0.3</v>
       </c>
-      <c r="E19" s="215" t="inlineStr">
+      <c r="E29" s="410" t="inlineStr">
         <is>
           <t>Theo bảng tiêu chí B, C</t>
         </is>
       </c>
-      <c r="F19" s="216" t="n"/>
-      <c r="G19" s="216" t="n"/>
-      <c r="H19" s="217" t="n">
+      <c r="F29" s="411" t="n"/>
+      <c r="G29" s="411" t="n"/>
+      <c r="H29" s="412" t="n">
         <v>10</v>
       </c>
-      <c r="I19" s="300">
-        <f>H19/C19</f>
-        <v/>
-      </c>
-      <c r="J19" s="219" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K19" s="219">
-        <f>$D19*$I19*20%</f>
-        <v/>
-      </c>
-      <c r="L19" s="220" t="n">
+      <c r="I29" s="413">
+        <f>H29/C29</f>
+        <v/>
+      </c>
+      <c r="J29" s="414" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K29" s="414">
+        <f>$D29*$I29*15%</f>
+        <v/>
+      </c>
+      <c r="L29" s="415" t="n">
         <v>9</v>
       </c>
-      <c r="M19" s="301">
-        <f>L19/C19</f>
-        <v/>
-      </c>
-      <c r="N19" s="167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O19" s="302">
-        <f>$D19*$M19*20%</f>
-        <v/>
-      </c>
-      <c r="P19" s="208" t="n"/>
-      <c r="Q19" s="223" t="n"/>
-      <c r="R19" s="224" t="n"/>
-      <c r="S19" s="225" t="n"/>
-      <c r="T19" s="225" t="n"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="212" t="n">
+      <c r="M29" s="416">
+        <f>L29/C29</f>
+        <v/>
+      </c>
+      <c r="N29" s="359" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O29" s="417">
+        <f>$D29*$M29*15%</f>
+        <v/>
+      </c>
+      <c r="P29" s="403" t="n"/>
+      <c r="Q29" s="418" t="n"/>
+      <c r="R29" s="419" t="n"/>
+      <c r="S29" s="419" t="n"/>
+      <c r="T29" s="419" t="n"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="407" t="n">
         <v>2</v>
       </c>
-      <c r="B20" s="213" t="inlineStr">
+      <c r="B30" s="408" t="inlineStr">
         <is>
           <t>Phối hợp trong công việc</t>
         </is>
       </c>
-      <c r="C20" s="167" t="n">
+      <c r="C30" s="359" t="n">
         <v>10</v>
       </c>
-      <c r="D20" s="214" t="n">
+      <c r="D30" s="409" t="n">
         <v>0.3</v>
       </c>
-      <c r="F20" s="216" t="n"/>
-      <c r="G20" s="216" t="n"/>
-      <c r="H20" s="217" t="n">
+      <c r="F30" s="411" t="n"/>
+      <c r="G30" s="411" t="n"/>
+      <c r="H30" s="412" t="n">
         <v>10</v>
       </c>
-      <c r="I20" s="300">
-        <f>H20/C20</f>
-        <v/>
-      </c>
-      <c r="J20" s="219" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K20" s="219">
-        <f>$D20*$I20*20%</f>
-        <v/>
-      </c>
-      <c r="L20" s="226" t="n">
+      <c r="I30" s="413">
+        <f>H30/C30</f>
+        <v/>
+      </c>
+      <c r="J30" s="414" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K30" s="414">
+        <f>$D30*$I30*15%</f>
+        <v/>
+      </c>
+      <c r="L30" s="389" t="n">
         <v>8</v>
       </c>
-      <c r="M20" s="301">
-        <f>L20/C20</f>
-        <v/>
-      </c>
-      <c r="N20" s="167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O20" s="302">
-        <f>$D20*$M20*20%</f>
-        <v/>
-      </c>
-      <c r="P20" s="208" t="n"/>
-      <c r="Q20" s="223" t="n"/>
-      <c r="R20" s="224" t="n"/>
-      <c r="S20" s="225" t="n"/>
-      <c r="T20" s="225" t="n"/>
-    </row>
-    <row r="21" ht="45.75" customHeight="1">
-      <c r="A21" s="212" t="n">
+      <c r="M30" s="416">
+        <f>L30/C30</f>
+        <v/>
+      </c>
+      <c r="N30" s="359" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O30" s="417">
+        <f>$D30*$M30*15%</f>
+        <v/>
+      </c>
+      <c r="P30" s="403" t="n"/>
+      <c r="Q30" s="418" t="n"/>
+      <c r="R30" s="419" t="n"/>
+      <c r="S30" s="419" t="n"/>
+      <c r="T30" s="419" t="n"/>
+    </row>
+    <row r="31" ht="45.75" customHeight="1">
+      <c r="A31" s="407" t="n">
         <v>3</v>
       </c>
-      <c r="B21" s="213" t="inlineStr">
+      <c r="B31" s="408" t="inlineStr">
         <is>
           <t>Tuân thủ kỷ luật trong công việc, chấp hành yêu cầu cấp trên và các quy định nội quy của Công ty</t>
         </is>
       </c>
-      <c r="C21" s="167" t="n">
+      <c r="C31" s="359" t="n">
         <v>10</v>
       </c>
-      <c r="D21" s="214" t="n">
+      <c r="D31" s="409" t="n">
         <v>0.4</v>
       </c>
-      <c r="E21" s="227" t="n"/>
-      <c r="F21" s="216" t="n"/>
-      <c r="G21" s="216" t="n"/>
-      <c r="H21" s="217" t="n">
+      <c r="E31" s="420" t="n"/>
+      <c r="F31" s="411" t="n"/>
+      <c r="G31" s="411" t="n"/>
+      <c r="H31" s="412" t="n">
         <v>10</v>
       </c>
-      <c r="I21" s="300">
-        <f>H21/C21</f>
-        <v/>
-      </c>
-      <c r="J21" s="219" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K21" s="219">
-        <f>$D21*$I21*20%</f>
-        <v/>
-      </c>
-      <c r="L21" s="226" t="n">
+      <c r="I31" s="413">
+        <f>H31/C31</f>
+        <v/>
+      </c>
+      <c r="J31" s="414" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K31" s="414">
+        <f>$D31*$I31*15%</f>
+        <v/>
+      </c>
+      <c r="L31" s="389" t="n">
         <v>10</v>
       </c>
-      <c r="M21" s="301">
-        <f>L21/C21</f>
-        <v/>
-      </c>
-      <c r="N21" s="167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O21" s="302">
-        <f>$D21*$M21*20%</f>
-        <v/>
-      </c>
-      <c r="P21" s="208" t="n"/>
-      <c r="Q21" s="223" t="n"/>
-      <c r="R21" s="224" t="n"/>
-      <c r="S21" s="225" t="n"/>
-      <c r="T21" s="225" t="n"/>
-    </row>
-    <row r="22" ht="30.75" customHeight="1">
-      <c r="A22" s="196" t="inlineStr">
+      <c r="M31" s="416">
+        <f>L31/C31</f>
+        <v/>
+      </c>
+      <c r="N31" s="359" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O31" s="417">
+        <f>$D31*$M31*15%</f>
+        <v/>
+      </c>
+      <c r="P31" s="403" t="n"/>
+      <c r="Q31" s="418" t="n"/>
+      <c r="R31" s="419" t="n"/>
+      <c r="S31" s="419" t="n"/>
+      <c r="T31" s="419" t="n"/>
+    </row>
+    <row r="32" ht="30.75" customHeight="1">
+      <c r="A32" s="391" t="inlineStr">
         <is>
           <t>C.</t>
         </is>
       </c>
-      <c r="B22" s="135" t="inlineStr">
+      <c r="B32" s="327" t="inlineStr">
         <is>
           <t>KỶ LUẬT LAO ĐỘNG (TỶ TRỌNG: 5%)</t>
         </is>
       </c>
-      <c r="C22" s="228" t="n"/>
-      <c r="D22" s="229">
-        <f>SUBTOTAL(9,D23:D26)</f>
-        <v/>
-      </c>
-      <c r="E22" s="230" t="n"/>
-      <c r="F22" s="285" t="inlineStr">
-        <is>
-          <t>= Trọng số * Điểm đạt * Tỷ trọng</t>
-        </is>
-      </c>
-      <c r="G22" s="231" t="n"/>
-      <c r="H22" s="232" t="n"/>
-      <c r="I22" s="232" t="n"/>
-      <c r="J22" s="232" t="n"/>
-      <c r="K22" s="303">
-        <f>SUBTOTAL(9,K23:K26)</f>
-        <v/>
-      </c>
-      <c r="L22" s="234" t="n"/>
-      <c r="M22" s="235" t="n"/>
-      <c r="N22" s="234" t="n"/>
-      <c r="O22" s="304">
-        <f>SUBTOTAL(9,O23:O26)</f>
-        <v/>
-      </c>
-      <c r="P22" s="208" t="n"/>
-      <c r="Q22" s="209" t="n"/>
-      <c r="R22" s="210" t="n"/>
-      <c r="S22" s="210" t="n"/>
-      <c r="T22" s="210" t="n"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="212" t="n">
+      <c r="C32" s="421" t="n"/>
+      <c r="D32" s="422">
+        <f>SUBTOTAL(9,D33:D36)</f>
+        <v/>
+      </c>
+      <c r="E32" s="423" t="n"/>
+      <c r="F32" s="395">
+        <f> Trọng số * Điểm đạt * Tỷ trọng</f>
+        <v/>
+      </c>
+      <c r="G32" s="424" t="n"/>
+      <c r="H32" s="425" t="n"/>
+      <c r="I32" s="425" t="n"/>
+      <c r="J32" s="425" t="n"/>
+      <c r="K32" s="426">
+        <f>SUBTOTAL(9,K33:K36)</f>
+        <v/>
+      </c>
+      <c r="L32" s="427" t="n"/>
+      <c r="M32" s="428" t="n"/>
+      <c r="N32" s="427" t="n"/>
+      <c r="O32" s="429">
+        <f>SUBTOTAL(9,O33:O36)</f>
+        <v/>
+      </c>
+      <c r="P32" s="403" t="n"/>
+      <c r="Q32" s="404" t="n"/>
+      <c r="R32" s="405" t="n"/>
+      <c r="S32" s="405" t="n"/>
+      <c r="T32" s="405" t="n"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="407" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="213" t="inlineStr">
+      <c r="B33" s="408" t="inlineStr">
         <is>
           <t>Đi muộn, về sớm</t>
         </is>
       </c>
-      <c r="C23" s="167" t="n">
+      <c r="C33" s="359" t="n">
         <v>10</v>
       </c>
-      <c r="D23" s="214" t="n">
+      <c r="D33" s="409" t="n">
         <v>0.3</v>
       </c>
-      <c r="E23" s="237" t="inlineStr">
+      <c r="E33" s="430" t="inlineStr">
         <is>
           <t>Theo bảng tiêu chí B, C</t>
         </is>
       </c>
-      <c r="F23" s="216" t="n"/>
-      <c r="G23" s="216" t="n"/>
-      <c r="H23" s="217" t="n">
+      <c r="F33" s="411" t="n"/>
+      <c r="G33" s="411" t="n"/>
+      <c r="H33" s="412" t="n">
         <v>10</v>
       </c>
-      <c r="I23" s="300">
-        <f>H23/C23</f>
-        <v/>
-      </c>
-      <c r="J23" s="219" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K23" s="305">
-        <f>$D23*$I23*5%</f>
-        <v/>
-      </c>
-      <c r="L23" s="167" t="n">
+      <c r="I33" s="413">
+        <f>H33/C33</f>
+        <v/>
+      </c>
+      <c r="J33" s="414" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K33" s="431">
+        <f>$D33*$I33*5%</f>
+        <v/>
+      </c>
+      <c r="L33" s="359" t="n">
         <v>7</v>
       </c>
-      <c r="M23" s="306">
-        <f>L23/C23</f>
-        <v/>
-      </c>
-      <c r="N23" s="167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O23" s="307">
-        <f>$D23*$M23*5%</f>
-        <v/>
-      </c>
-      <c r="P23" s="208" t="n"/>
-      <c r="Q23" s="223" t="n"/>
-      <c r="R23" s="224" t="n"/>
-      <c r="S23" s="225" t="n"/>
-      <c r="T23" s="225" t="n"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="212" t="n">
+      <c r="M33" s="432">
+        <f>L33/C33</f>
+        <v/>
+      </c>
+      <c r="N33" s="359" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O33" s="433">
+        <f>$D33*$M33*5%</f>
+        <v/>
+      </c>
+      <c r="P33" s="403" t="n"/>
+      <c r="Q33" s="418" t="n"/>
+      <c r="R33" s="419" t="n"/>
+      <c r="S33" s="419" t="n"/>
+      <c r="T33" s="419" t="n"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="407" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="213" t="inlineStr">
+      <c r="B34" s="408" t="inlineStr">
         <is>
           <t>Nghỉ không phép</t>
         </is>
       </c>
-      <c r="C24" s="167" t="n">
+      <c r="C34" s="359" t="n">
         <v>10</v>
       </c>
-      <c r="D24" s="214" t="n">
+      <c r="D34" s="409" t="n">
         <v>0.3</v>
       </c>
-      <c r="F24" s="216" t="n"/>
-      <c r="G24" s="216" t="n"/>
-      <c r="H24" s="217" t="n">
+      <c r="F34" s="411" t="n"/>
+      <c r="G34" s="411" t="n"/>
+      <c r="H34" s="412" t="n">
         <v>10</v>
       </c>
-      <c r="I24" s="300">
-        <f>H24/C24</f>
-        <v/>
-      </c>
-      <c r="J24" s="219" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K24" s="305">
-        <f>$D24*$I24*5%</f>
-        <v/>
-      </c>
-      <c r="L24" s="167" t="n">
+      <c r="I34" s="413">
+        <f>H34/C34</f>
+        <v/>
+      </c>
+      <c r="J34" s="414" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K34" s="431">
+        <f>$D34*$I34*5%</f>
+        <v/>
+      </c>
+      <c r="L34" s="359" t="n">
         <v>7</v>
       </c>
-      <c r="M24" s="306">
-        <f>L24/C24</f>
-        <v/>
-      </c>
-      <c r="N24" s="167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O24" s="307">
-        <f>$D24*$M24*5%</f>
-        <v/>
-      </c>
-      <c r="P24" s="208" t="n"/>
-      <c r="Q24" s="223" t="n"/>
-      <c r="R24" s="224" t="n"/>
-      <c r="S24" s="225" t="n"/>
-      <c r="T24" s="225" t="n"/>
-    </row>
-    <row r="25" ht="30.75" customHeight="1">
-      <c r="A25" s="212" t="n">
+      <c r="M34" s="432">
+        <f>L34/C34</f>
+        <v/>
+      </c>
+      <c r="N34" s="359" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O34" s="433">
+        <f>$D34*$M34*5%</f>
+        <v/>
+      </c>
+      <c r="P34" s="403" t="n"/>
+      <c r="Q34" s="418" t="n"/>
+      <c r="R34" s="419" t="n"/>
+      <c r="S34" s="419" t="n"/>
+      <c r="T34" s="419" t="n"/>
+    </row>
+    <row r="35" ht="30.75" customHeight="1">
+      <c r="A35" s="407" t="n">
         <v>3</v>
       </c>
-      <c r="B25" s="213" t="inlineStr">
+      <c r="B35" s="408" t="inlineStr">
         <is>
           <t>Quên không chấm công (check in và check out)</t>
         </is>
       </c>
-      <c r="C25" s="167" t="n">
+      <c r="C35" s="359" t="n">
         <v>10</v>
       </c>
-      <c r="D25" s="214" t="n">
+      <c r="D35" s="409" t="n">
         <v>0.3</v>
       </c>
-      <c r="F25" s="216" t="n"/>
-      <c r="G25" s="216" t="n"/>
-      <c r="H25" s="217" t="n">
+      <c r="F35" s="411" t="n"/>
+      <c r="G35" s="411" t="n"/>
+      <c r="H35" s="412" t="n">
         <v>10</v>
       </c>
-      <c r="I25" s="300">
-        <f>H25/C25</f>
-        <v/>
-      </c>
-      <c r="J25" s="219" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K25" s="305">
-        <f>$D25*$I25*5%</f>
-        <v/>
-      </c>
-      <c r="L25" s="167" t="n">
+      <c r="I35" s="413">
+        <f>H35/C35</f>
+        <v/>
+      </c>
+      <c r="J35" s="414" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K35" s="431">
+        <f>$D35*$I35*5%</f>
+        <v/>
+      </c>
+      <c r="L35" s="359" t="n">
         <v>6</v>
       </c>
-      <c r="M25" s="306">
-        <f>L25/C25</f>
-        <v/>
-      </c>
-      <c r="N25" s="167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O25" s="307">
-        <f>$D25*$M25*5%</f>
-        <v/>
-      </c>
-      <c r="P25" s="208" t="n"/>
-      <c r="Q25" s="223" t="n"/>
-      <c r="R25" s="224" t="n"/>
-      <c r="S25" s="225" t="n"/>
-      <c r="T25" s="225" t="n"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="241" t="n">
+      <c r="M35" s="432">
+        <f>L35/C35</f>
+        <v/>
+      </c>
+      <c r="N35" s="359" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O35" s="433">
+        <f>$D35*$M35*5%</f>
+        <v/>
+      </c>
+      <c r="P35" s="403" t="n"/>
+      <c r="Q35" s="418" t="n"/>
+      <c r="R35" s="419" t="n"/>
+      <c r="S35" s="419" t="n"/>
+      <c r="T35" s="419" t="n"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="434" t="n">
         <v>4</v>
       </c>
-      <c r="B26" s="242" t="inlineStr">
+      <c r="B36" s="435" t="inlineStr">
         <is>
           <t>Xanh-Sạch-Đẹp</t>
         </is>
       </c>
-      <c r="C26" s="167" t="n">
+      <c r="C36" s="359" t="n">
         <v>10</v>
       </c>
-      <c r="D26" s="214" t="n">
+      <c r="D36" s="409" t="n">
         <v>0.1</v>
       </c>
-      <c r="E26" s="62" t="n"/>
-      <c r="F26" s="216" t="n"/>
-      <c r="G26" s="216" t="n"/>
-      <c r="H26" s="217" t="n">
+      <c r="E36" s="62" t="n"/>
+      <c r="F36" s="411" t="n"/>
+      <c r="G36" s="411" t="n"/>
+      <c r="H36" s="412" t="n">
         <v>10</v>
       </c>
-      <c r="I26" s="300">
-        <f>H26/C26</f>
-        <v/>
-      </c>
-      <c r="J26" s="219" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K26" s="305">
-        <f>$D26*$I26*5%</f>
-        <v/>
-      </c>
-      <c r="L26" s="167" t="n">
+      <c r="I36" s="413">
+        <f>H36/C36</f>
+        <v/>
+      </c>
+      <c r="J36" s="414" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K36" s="431">
+        <f>$D36*$I36*5%</f>
+        <v/>
+      </c>
+      <c r="L36" s="359" t="n">
         <v>6</v>
       </c>
-      <c r="M26" s="306">
-        <f>L26/C26</f>
-        <v/>
-      </c>
-      <c r="N26" s="167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O26" s="307">
-        <f>$D26*$M26*5%</f>
-        <v/>
-      </c>
-      <c r="P26" s="208" t="n"/>
-      <c r="Q26" s="223" t="n"/>
-      <c r="R26" s="224" t="n"/>
-      <c r="S26" s="225" t="n"/>
-      <c r="T26" s="225" t="n"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="243" t="inlineStr">
+      <c r="M36" s="432">
+        <f>L36/C36</f>
+        <v/>
+      </c>
+      <c r="N36" s="359" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O36" s="433">
+        <f>$D36*$M36*5%</f>
+        <v/>
+      </c>
+      <c r="P36" s="403" t="n"/>
+      <c r="Q36" s="418" t="n"/>
+      <c r="R36" s="419" t="n"/>
+      <c r="S36" s="419" t="n"/>
+      <c r="T36" s="419" t="n"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="436" t="inlineStr">
         <is>
           <t>TỔNG</t>
         </is>
       </c>
-      <c r="B27" s="127" t="n"/>
-      <c r="C27" s="27" t="n"/>
-      <c r="D27" s="244" t="n"/>
-      <c r="E27" s="245" t="n"/>
-      <c r="F27" s="244" t="n"/>
-      <c r="G27" s="244" t="n"/>
-      <c r="H27" s="244" t="n"/>
-      <c r="I27" s="244" t="n"/>
-      <c r="J27" s="244" t="n"/>
-      <c r="K27" s="309">
-        <f>SUM(K22,K18,K3)</f>
-        <v/>
-      </c>
-      <c r="L27" s="309" t="n"/>
-      <c r="M27" s="247" t="n"/>
-      <c r="N27" s="247" t="n"/>
-      <c r="O27" s="309">
-        <f>SUM(O22,O18,O3)</f>
-        <v/>
-      </c>
-      <c r="P27" s="208" t="n"/>
-      <c r="Q27" s="248" t="n"/>
-      <c r="R27" s="249" t="n"/>
-      <c r="S27" s="249" t="n"/>
-      <c r="T27" s="250" t="n"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="251" t="inlineStr">
+      <c r="B37" s="127" t="n"/>
+      <c r="C37" s="27" t="n"/>
+      <c r="D37" s="437" t="n"/>
+      <c r="E37" s="438" t="n"/>
+      <c r="F37" s="437" t="n"/>
+      <c r="G37" s="437" t="n"/>
+      <c r="H37" s="437" t="n"/>
+      <c r="I37" s="437" t="n"/>
+      <c r="J37" s="437" t="n"/>
+      <c r="K37" s="439">
+        <f>SUM(K32,K28,K3)</f>
+        <v/>
+      </c>
+      <c r="L37" s="439" t="n"/>
+      <c r="M37" s="440" t="n"/>
+      <c r="N37" s="440" t="n"/>
+      <c r="O37" s="439">
+        <f>SUM(O32,O28,O3)</f>
+        <v/>
+      </c>
+      <c r="P37" s="403" t="n"/>
+      <c r="Q37" s="441" t="n"/>
+      <c r="R37" s="442" t="n"/>
+      <c r="S37" s="442" t="n"/>
+      <c r="T37" s="443" t="n"/>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="444" t="inlineStr">
         <is>
           <t>TỔNG CỘNG= ((Nhân viên đánh giá *1)+(CBQL đánh giá *2))/3</t>
         </is>
       </c>
-      <c r="B28" s="252" t="n"/>
-      <c r="C28" s="253" t="n"/>
-      <c r="D28" s="253" t="n"/>
-      <c r="E28" s="253" t="n"/>
-      <c r="F28" s="253" t="n"/>
-      <c r="G28" s="253" t="n"/>
-      <c r="H28" s="310">
-        <f>(K27+O27*2)/3</f>
-        <v/>
-      </c>
-      <c r="I28" s="127" t="n"/>
-      <c r="J28" s="127" t="n"/>
-      <c r="K28" s="127" t="n"/>
-      <c r="L28" s="127" t="n"/>
-      <c r="M28" s="127" t="n"/>
-      <c r="N28" s="127" t="n"/>
-      <c r="O28" s="27" t="n"/>
-      <c r="P28" s="255" t="n"/>
-      <c r="Q28" s="255" t="n"/>
-      <c r="R28" s="255" t="n"/>
-      <c r="S28" s="255" t="n"/>
-      <c r="T28" s="256" t="n"/>
+      <c r="B38" s="445" t="n"/>
+      <c r="C38" s="446" t="n"/>
+      <c r="D38" s="446" t="n"/>
+      <c r="E38" s="446" t="n"/>
+      <c r="F38" s="446" t="n"/>
+      <c r="G38" s="446" t="n"/>
+      <c r="H38" s="447">
+        <f>(K37 + O37*2)/3</f>
+        <v/>
+      </c>
+      <c r="I38" s="127" t="n"/>
+      <c r="J38" s="127" t="n"/>
+      <c r="K38" s="127" t="n"/>
+      <c r="L38" s="127" t="n"/>
+      <c r="M38" s="127" t="n"/>
+      <c r="N38" s="127" t="n"/>
+      <c r="O38" s="27" t="n"/>
+      <c r="P38" s="448" t="n"/>
+      <c r="Q38" s="448" t="n"/>
+      <c r="R38" s="448" t="n"/>
+      <c r="S38" s="448" t="n"/>
+      <c r="T38" s="449" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="E23:E26"/>
-    <mergeCell ref="A27:C27"/>
+  <mergeCells count="13">
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="H38:O38"/>
     <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="F24:F27"/>
+    <mergeCell ref="E29:E31"/>
+    <mergeCell ref="G1:G2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H28:O28"/>
     <mergeCell ref="H1:K1"/>
     <mergeCell ref="L1:O1"/>
+    <mergeCell ref="E33:E36"/>
+    <mergeCell ref="G24:G27"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T33"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col width="9.140625" customWidth="1" min="1" max="1"/>
+    <col width="37.28515625" customWidth="1" min="2" max="2"/>
+    <col width="19.140625" customWidth="1" min="3" max="3"/>
+    <col width="17.7109375" customWidth="1" min="4" max="4"/>
+    <col width="67.7109375" customWidth="1" min="5" max="5"/>
+    <col width="46.7109375" customWidth="1" min="6" max="6"/>
+    <col width="36.140625" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18.7109375" customWidth="1" min="10" max="10"/>
+    <col width="27.42578125" customWidth="1" min="11" max="11"/>
+    <col width="18.28515625" customWidth="1" min="12" max="12"/>
+    <col width="18.42578125" customWidth="1" min="13" max="13"/>
+    <col width="17.7109375" customWidth="1" min="14" max="14"/>
+    <col width="35.42578125" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30.75" customHeight="1">
+      <c r="A1" s="315" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B1" s="315" t="inlineStr">
+        <is>
+          <t>CHỈ TIÊU</t>
+        </is>
+      </c>
+      <c r="C1" s="315" t="inlineStr">
+        <is>
+          <t>Kế hoạch (Điểm)</t>
+        </is>
+      </c>
+      <c r="D1" s="315" t="inlineStr">
+        <is>
+          <t>Trọng số</t>
+        </is>
+      </c>
+      <c r="E1" s="316" t="inlineStr">
+        <is>
+          <t>MÔ TẢ THƯỚC ĐO CHỈ TIÊU</t>
+        </is>
+      </c>
+      <c r="F1" s="317" t="inlineStr">
+        <is>
+          <t>Công thức Tính</t>
+        </is>
+      </c>
+      <c r="G1" s="317" t="inlineStr">
+        <is>
+          <t>Công thức Tính (Thang điểm 10)</t>
+        </is>
+      </c>
+      <c r="H1" s="318" t="inlineStr">
+        <is>
+          <t>NHÂN VIÊN ĐÁNH GIÁ</t>
+        </is>
+      </c>
+      <c r="I1" s="127" t="n"/>
+      <c r="J1" s="127" t="n"/>
+      <c r="K1" s="27" t="n"/>
+      <c r="L1" s="318" t="inlineStr">
+        <is>
+          <t>CBQL ĐÁNH GIÁ</t>
+        </is>
+      </c>
+      <c r="M1" s="127" t="n"/>
+      <c r="N1" s="127" t="n"/>
+      <c r="O1" s="27" t="n"/>
+      <c r="P1" s="319" t="n"/>
+      <c r="Q1" s="319" t="n"/>
+      <c r="R1" s="319" t="n"/>
+      <c r="S1" s="319" t="n"/>
+    </row>
+    <row r="2" ht="61.5" customHeight="1">
+      <c r="A2" s="320" t="n"/>
+      <c r="B2" s="315" t="inlineStr">
+        <is>
+          <t>Hạng mục</t>
+        </is>
+      </c>
+      <c r="C2" s="320" t="n"/>
+      <c r="D2" s="320" t="n"/>
+      <c r="E2" s="321" t="n"/>
+      <c r="F2" s="322" t="n"/>
+      <c r="G2" s="322" t="n"/>
+      <c r="H2" s="323" t="inlineStr">
+        <is>
+          <t>Thực đạt (Tiêu chí B,C)</t>
+        </is>
+      </c>
+      <c r="I2" s="323" t="inlineStr">
+        <is>
+          <t>Điểm đạt = Thực đạt/Kế hoạch (Tiêu chí B,C)</t>
+        </is>
+      </c>
+      <c r="J2" s="323" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành (Tiêu chí A)</t>
+        </is>
+      </c>
+      <c r="K2" s="324" t="inlineStr">
+        <is>
+          <t>Điểm KPIs (Tính theo công thức của tùng loại tiêu chí)</t>
+        </is>
+      </c>
+      <c r="L2" s="325" t="inlineStr">
+        <is>
+          <t>Thực đạt (Tiêu chí B,C)</t>
+        </is>
+      </c>
+      <c r="M2" s="325" t="inlineStr">
+        <is>
+          <t>Điểm đạt = Thực đạt/Kế hoạch (Tiêu chí B,C)</t>
+        </is>
+      </c>
+      <c r="N2" s="325" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành (Tiêu chí A)</t>
+        </is>
+      </c>
+      <c r="O2" s="318" t="inlineStr">
+        <is>
+          <t>Điểm KPIs (Tính theo công thức của tùng loại tiêu chí)</t>
+        </is>
+      </c>
+      <c r="P2" s="319" t="n"/>
+      <c r="Q2" s="319" t="n"/>
+      <c r="R2" s="319" t="n"/>
+      <c r="S2" s="319" t="n"/>
+    </row>
+    <row r="3" ht="45.75" customHeight="1">
+      <c r="A3" s="326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A. </t>
+        </is>
+      </c>
+      <c r="B3" s="327" t="inlineStr">
+        <is>
+          <t>HIỆU QUẢ CÔNG VIỆC (TỶ TRỌNG: Max = 100%)</t>
+        </is>
+      </c>
+      <c r="C3" s="328" t="n"/>
+      <c r="D3" s="328" t="n"/>
+      <c r="E3" s="328" t="n"/>
+      <c r="F3" s="329" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> = 35% * Delivery + 20% * Quality + 10% * Reliability + 10% * Collaboration + 5% * Growth + 20% * Impact Bonus</t>
+        </is>
+      </c>
+      <c r="G3" s="328" t="n"/>
+      <c r="H3" s="330" t="n"/>
+      <c r="I3" s="330" t="n"/>
+      <c r="J3" s="330" t="n"/>
+      <c r="K3" s="331">
+        <f>(0.35*K4+0.2*K9+0.1*K15+0.1*K16+0.05*K17+0.2*K18)/10</f>
+        <v/>
+      </c>
+      <c r="L3" s="331" t="n"/>
+      <c r="M3" s="330" t="n"/>
+      <c r="N3" s="330" t="n"/>
+      <c r="O3" s="331">
+        <f>(0.35*O4+0.2*O9+0.1*O15+0.1*O16+0.05*O17+0.2*O18)/10</f>
+        <v/>
+      </c>
+      <c r="P3" s="319" t="n"/>
+      <c r="Q3" s="319" t="n"/>
+      <c r="R3" s="319" t="n"/>
+      <c r="S3" s="319" t="n"/>
+    </row>
+    <row r="4" ht="61.5" customHeight="1">
+      <c r="A4" s="332" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="333" t="inlineStr">
+        <is>
+          <t>Delivery KPI</t>
+        </is>
+      </c>
+      <c r="C4" s="334" t="n"/>
+      <c r="D4" s="335" t="n"/>
+      <c r="E4" s="336" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiêu chí: Delivery phản ánh khả năng chuyển giao công việc đã cam kết thành kết quả có giá trị.
+</t>
+        </is>
+      </c>
+      <c r="F4" s="337" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> = 40% × Commitment Achievement + 25% × Schedule Performance + 20% × Work Throughput + 15% × Delivery Ownership</t>
+        </is>
+      </c>
+      <c r="G4" s="338" t="n"/>
+      <c r="H4" s="339" t="n"/>
+      <c r="I4" s="339" t="n"/>
+      <c r="J4" s="339" t="n"/>
+      <c r="K4" s="340">
+        <f>0.4*K5+0.25*K6+0.2*K7+0.15*K8</f>
+        <v/>
+      </c>
+      <c r="L4" s="341" t="n"/>
+      <c r="M4" s="342" t="n"/>
+      <c r="N4" s="342" t="n"/>
+      <c r="O4" s="342">
+        <f>0.4*O5+0.25*O6+0.2*O7+0.15*O8</f>
+        <v/>
+      </c>
+      <c r="P4" s="319" t="n"/>
+      <c r="Q4" s="319" t="n"/>
+      <c r="R4" s="319" t="n"/>
+      <c r="S4" s="319" t="n"/>
+    </row>
+    <row r="5" ht="137.25" customHeight="1">
+      <c r="A5" s="343" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="B5" s="344" t="inlineStr">
+        <is>
+          <t>Commitment Achievement</t>
+        </is>
+      </c>
+      <c r="C5" s="345" t="n"/>
+      <c r="D5" s="346" t="n"/>
+      <c r="E5" s="347" t="inlineStr">
+        <is>
+          <t>- Tiêu chí: Hoàn thành công việc đã cam kết
+- Đánh giá khả năng hoàn thành các Jira Task/Ticket đã cam kết.
+Không tính:
+- Ticket bị hủy
+- Scope thay đổi do PO/BA
+- Công việc chưa đủ điều kiện triển khai
+- Blocker ngoài khả năng kiểm soát</t>
+        </is>
+      </c>
+      <c r="F5" s="348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Công thức: Tỷ lệ hoàn thành -- Điểm
+≥100%     --	100
+95–99%   --	95
+90–94%	 -- 90
+80–89%	 -- 80
+&lt;80%	 -- 60
+</t>
+        </is>
+      </c>
+      <c r="G5" s="348" t="inlineStr">
+        <is>
+          <t>Công thức: Tỷ lệ hoàn thành -- Điểm
+≥100%     --	10
+95–99%   --	9.5
+90–94%	 -- 9.0
+80–89%	 -- 8.0
+&lt;80%	 -- 6.0</t>
+        </is>
+      </c>
+      <c r="H5" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I5" s="350" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J5" s="349" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="351" t="n">
+        <v>10</v>
+      </c>
+      <c r="L5" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M5" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N5" s="349" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="O5" s="351" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P5" s="319" t="n"/>
+      <c r="Q5" s="319" t="n"/>
+      <c r="R5" s="319" t="n"/>
+      <c r="S5" s="319" t="n"/>
+    </row>
+    <row r="6" ht="121.5" customHeight="1">
+      <c r="A6" s="343" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="B6" s="344" t="inlineStr">
+        <is>
+          <t>Schedule Performance</t>
+        </is>
+      </c>
+      <c r="C6" s="345" t="n"/>
+      <c r="D6" s="346" t="n"/>
+      <c r="E6" s="352" t="inlineStr">
+        <is>
+          <t>-Tiêu chí: Hoàn thành đúng thời hạn
+- Đánh giá mức độ hoàn thành đúng thời hạn.
+Không tính:
+- Delay do Requirement thay đổi
+- Delay do hạ tầng
+- Delay do phụ thuộc team khác</t>
+        </is>
+      </c>
+      <c r="F6" s="348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Công thức: On-time Rate	Điểm
+≥95%	100
+90–94%	95
+80–89%	85
+70–79%	75
+&lt;70%	60
+</t>
+        </is>
+      </c>
+      <c r="G6" s="348" t="inlineStr">
+        <is>
+          <t>On-time Rate --- Điểm
+≥95%	--  10
+90–94%	 -- 9.5
+80–89%	 --  8.5
+70–79%	 --  7.5
+&lt;70%	 --   6.0</t>
+        </is>
+      </c>
+      <c r="H6" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I6" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J6" s="349" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="351" t="n">
+        <v>10</v>
+      </c>
+      <c r="L6" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M6" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N6" s="349" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="O6" s="351" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P6" s="319" t="n"/>
+      <c r="Q6" s="319" t="n"/>
+      <c r="R6" s="319" t="n"/>
+      <c r="S6" s="319" t="n"/>
+    </row>
+    <row r="7" ht="91.5" customHeight="1">
+      <c r="A7" s="343" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="B7" s="344" t="inlineStr">
+        <is>
+          <t>Work Throughput</t>
+        </is>
+      </c>
+      <c r="C7" s="345" t="n"/>
+      <c r="D7" s="346" t="n"/>
+      <c r="E7" s="352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiêu chí: Khối lượng công việc hoàn thành theo Scope Score.
+Đánh giá công việc hoàn thành dựa trên level/ cấp bậc nhân sự
+Notes: 
+- Không sử dụng số lượng Task hoặc Ticket.
+- Đề xuất sử dụng Scope Score.
+</t>
+        </is>
+      </c>
+      <c r="F7" s="353" t="inlineStr">
+        <is>
+          <t>Công thức: Throughput	Điểm
+≥95%	100
+90–94%	95
+80–89%	85
+&lt;80%	70</t>
+        </is>
+      </c>
+      <c r="G7" s="353" t="inlineStr">
+        <is>
+          <t>Throughput ---  Điểm
+≥95%	   10
+90–94%	    9.5
+80–89%	    8.5
+&lt;80%	    7.0</t>
+        </is>
+      </c>
+      <c r="H7" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I7" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J7" s="354" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="355" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M7" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N7" s="349" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O7" s="351" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P7" s="319" t="n"/>
+      <c r="Q7" s="319" t="n"/>
+      <c r="R7" s="319" t="n"/>
+      <c r="S7" s="319" t="n"/>
+    </row>
+    <row r="8" ht="167.25" customHeight="1">
+      <c r="A8" s="343" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="B8" s="344" t="inlineStr">
+        <is>
+          <t>Delivery Ownership</t>
+        </is>
+      </c>
+      <c r="C8" s="345" t="n"/>
+      <c r="D8" s="346" t="n"/>
+      <c r="E8" s="356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiêu chí: Chủ động xử lý và đảm bảo tiến độ
+Đánh giá mức độ chủ động trong quá trình thực hiện.
+</t>
+        </is>
+      </c>
+      <c r="F8" s="357" t="inlineStr">
+        <is>
+          <t>Công thức: Manager đánh giá theo Rubric.
+Mức	   -    Tiêu chí
+5	Luôn chủ động xử lý blocker, cảnh báo rủi ro sớm, đề xuất phương án khả thi
+4	Chủ động trong hầu hết tình huống
+3	Hoàn thành công việc được giao, biết báo cáo khi gặp khó khăn
+2	Thường xuyên cần nhắc nhở
+1	Bị động, ảnh hưởng đến tiến độ chung</t>
+        </is>
+      </c>
+      <c r="G8" s="357" t="inlineStr">
+        <is>
+          <t>Mức	   -    Tiêu chí
+10 --	Luôn chủ động xử lý blocker, cảnh báo rủi ro sớm, đề xuất phương án khả thi
+9--	Chủ động trong hầu hết tình huống
+7.5--	Hoàn thành công việc được giao, biết báo cáo khi gặp khó khăn
+5--	Thường xuyên cần nhắc nhở
+2--	Bị động, ảnh hưởng đến tiến độ chung</t>
+        </is>
+      </c>
+      <c r="H8" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I8" s="358" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J8" s="359" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K8" s="360" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M8" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N8" s="350" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O8" s="351" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P8" s="319" t="n"/>
+      <c r="Q8" s="319" t="n"/>
+      <c r="R8" s="319" t="n"/>
+      <c r="S8" s="319" t="n"/>
+    </row>
+    <row r="9" ht="61.5" customHeight="1">
+      <c r="A9" s="332" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="361" t="inlineStr">
+        <is>
+          <t>Quality KPI</t>
+        </is>
+      </c>
+      <c r="C9" s="362" t="n"/>
+      <c r="D9" s="335" t="n"/>
+      <c r="E9" s="363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiêu chí: Quality phản ánh khả năng tạo ra phần mềm đáp ứng yêu cầu chất lượng trong toàn bộ SDLC, không chỉ là số lượng bug sau khi release.
+</t>
+        </is>
+      </c>
+      <c r="F9" s="364" t="inlineStr">
+        <is>
+          <t>Công thức: Quality Score = 25% × Code Quality + 20% × Testing Quality + 15% × Build &amp; Release Quality + 25% × Production Quality + 15% × Quality Process Compliance</t>
+        </is>
+      </c>
+      <c r="G9" s="365" t="n"/>
+      <c r="H9" s="339" t="n"/>
+      <c r="I9" s="339" t="n"/>
+      <c r="J9" s="366" t="n"/>
+      <c r="K9" s="367">
+        <f>0.25*K10+0.2*K11+0.15*K12+0.25*K13+0.15*K14</f>
+        <v/>
+      </c>
+      <c r="L9" s="368" t="n"/>
+      <c r="M9" s="342" t="n"/>
+      <c r="N9" s="342" t="n"/>
+      <c r="O9" s="342">
+        <f>0.25*O10+0.2*O11+0.15*O12+0.25*O13+0.15*O14</f>
+        <v/>
+      </c>
+      <c r="P9" s="319" t="n"/>
+      <c r="Q9" s="319" t="n"/>
+      <c r="R9" s="319" t="n"/>
+      <c r="S9" s="319" t="n"/>
+    </row>
+    <row r="10" ht="107.25" customHeight="1">
+      <c r="A10" s="343" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="B10" s="369" t="inlineStr">
+        <is>
+          <t>Code Quality</t>
+        </is>
+      </c>
+      <c r="C10" s="370" t="n"/>
+      <c r="D10" s="346" t="n"/>
+      <c r="E10" s="371" t="inlineStr">
+        <is>
+          <t>Đánh giá chất lượng mã nguồn trước khi merge.</t>
+        </is>
+      </c>
+      <c r="F10" s="353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Điểm    ---    Đánh giá
+95–100	Xuất sắc
+90–94	Tốt
+80–89	Đạt
+70–79	Cần cải thiện
+&lt;70	Không đạt
+</t>
+        </is>
+      </c>
+      <c r="G10" s="348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Điểm    ---    Đánh giá
+9.5–10	Xuất sắc
+8.5–9.0	Tốt
+7.0–8.0	Đạt
+5.0–6.5	Cần cải thiện
+&lt;4.5	Không đạt
+</t>
+        </is>
+      </c>
+      <c r="H10" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I10" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J10" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K10" s="372" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M10" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N10" s="351" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O10" s="372" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P10" s="319" t="n"/>
+      <c r="Q10" s="319" t="n"/>
+      <c r="R10" s="319" t="n"/>
+      <c r="S10" s="319" t="n"/>
+    </row>
+    <row r="11" ht="107.25" customHeight="1">
+      <c r="A11" s="343" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="B11" s="369" t="inlineStr">
+        <is>
+          <t>Testing Quality</t>
+        </is>
+      </c>
+      <c r="C11" s="370" t="n"/>
+      <c r="D11" s="346" t="n"/>
+      <c r="E11" s="373" t="inlineStr">
+        <is>
+          <t>Đánh giá chất lượng kiểm thử (self test)
+Tham số đầu vào:
+- Unit Test Coverage
+- Integration Test
+- Regression Test
+- Test Pass Rate
+- Flaky Test</t>
+        </is>
+      </c>
+      <c r="F11" s="374" t="n"/>
+      <c r="G11" s="374" t="n"/>
+      <c r="H11" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I11" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J11" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K11" s="372" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M11" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N11" s="351" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O11" s="372" t="n">
+        <v>9</v>
+      </c>
+      <c r="P11" s="319" t="n"/>
+      <c r="Q11" s="319" t="n"/>
+      <c r="R11" s="319" t="n"/>
+      <c r="S11" s="319" t="n"/>
+    </row>
+    <row r="12" ht="91.5" customHeight="1">
+      <c r="A12" s="343" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="B12" s="369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Build &amp; Release Quality </t>
+        </is>
+      </c>
+      <c r="C12" s="370" t="n"/>
+      <c r="D12" s="346" t="n"/>
+      <c r="E12" s="375" t="inlineStr">
+        <is>
+          <t>Đánh giá chất lượng build.
+Tham số:
+- Build Success Rate
+- Failed Build
+- Rollback
+- Release Checklist</t>
+        </is>
+      </c>
+      <c r="F12" s="348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Điều kiện  ---	Điểm
+Không lỗi build, không rollback	100
+1 failed build nhỏ	95
+Nhiều failed build	80
+Rollback Production	60
+</t>
+        </is>
+      </c>
+      <c r="G12" s="348" t="inlineStr">
+        <is>
+          <t>Điều kiện  ---	Điểm
+Không lỗi build, không rollback	-- 10
+1 failed build nhỏ	---   9.5
+Nhiều failed build --  	8.0
+Rollback Production  ---  6.0</t>
+        </is>
+      </c>
+      <c r="H12" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I12" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J12" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K12" s="372" t="n">
+        <v>10</v>
+      </c>
+      <c r="L12" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M12" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N12" s="351" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O12" s="372" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P12" s="319" t="n"/>
+      <c r="Q12" s="319" t="n"/>
+      <c r="R12" s="319" t="n"/>
+      <c r="S12" s="319" t="n"/>
+    </row>
+    <row r="13" ht="107.25" customHeight="1">
+      <c r="A13" s="343" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="B13" s="369" t="inlineStr">
+        <is>
+          <t>Production Quality</t>
+        </is>
+      </c>
+      <c r="C13" s="370" t="n"/>
+      <c r="D13" s="346" t="n"/>
+      <c r="E13" s="375" t="inlineStr">
+        <is>
+          <t>Đây là nhóm phản ánh Outcome của Quality.
+Tham số:
+- Escaped Defects
+- Critical Bug
+- P1 Incident
+- Customer Complaint</t>
+        </is>
+      </c>
+      <c r="F13" s="353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Điều kiện	Điểm
+Không Critical Bug	100
+1 Minor Bug	95
+2 Minor Bug	90
+Có Critical Bug	70
+Có P1 Incident	50
+</t>
+        </is>
+      </c>
+      <c r="G13" s="353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Điều kiện ---	Điểm
+Không Critical Bug ---	10
+1 Minor Bug	--- 9.5
+2 Minor Bug	--- 9.0
+Có Critical Bug ---	7.0
+Có P1 Incident ---	5.0
+</t>
+        </is>
+      </c>
+      <c r="H13" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I13" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J13" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K13" s="372" t="n">
+        <v>10</v>
+      </c>
+      <c r="L13" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M13" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N13" s="351" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O13" s="372" t="n">
+        <v>9</v>
+      </c>
+      <c r="P13" s="319" t="n"/>
+      <c r="Q13" s="319" t="n"/>
+      <c r="R13" s="319" t="n"/>
+      <c r="S13" s="319" t="n"/>
+    </row>
+    <row r="14" ht="121.5" customHeight="1">
+      <c r="A14" s="343" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="B14" s="369" t="inlineStr">
+        <is>
+          <t>Quality Process Compliance</t>
+        </is>
+      </c>
+      <c r="C14" s="370" t="n"/>
+      <c r="D14" s="346" t="n"/>
+      <c r="E14" s="375" t="inlineStr">
+        <is>
+          <t>Đánh giá việc tuân thủ Quality Practice.
+Tham số: 
+- Pull Request Checklist
+- Definition of Done
+- Coding Standard
+- Review Checklist
+- Documentation</t>
+        </is>
+      </c>
+      <c r="F14" s="357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mức	Mô tả
+5	Luôn tuân thủ đầy đủ quy trình
+4	Có thiếu sót nhỏ
+3	Đôi khi bỏ qua checklist
+2	Thường xuyên vi phạm
+1	Không tuân thủ quy trình
+</t>
+        </is>
+      </c>
+      <c r="G14" s="357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mức   ---	Mô tả
+10	Luôn tuân thủ đầy đủ quy trình
+9	Có thiếu sót nhỏ
+7.5	Đôi khi bỏ qua checklist
+5	Thường xuyên vi phạm
+2	Không tuân thủ quy trình
+</t>
+        </is>
+      </c>
+      <c r="H14" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I14" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J14" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K14" s="372" t="n">
+        <v>10</v>
+      </c>
+      <c r="L14" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M14" s="349" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N14" s="351" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O14" s="376" t="n">
+        <v>9</v>
+      </c>
+      <c r="P14" s="319" t="n"/>
+      <c r="Q14" s="319" t="n"/>
+      <c r="R14" s="319" t="n"/>
+      <c r="S14" s="319" t="n"/>
+    </row>
+    <row r="15" ht="121.5" customHeight="1">
+      <c r="A15" s="332" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="361" t="inlineStr">
+        <is>
+          <t>Reliability KPI</t>
+        </is>
+      </c>
+      <c r="C15" s="377" t="n"/>
+      <c r="D15" s="378" t="n"/>
+      <c r="E15" s="336" t="inlineStr">
+        <is>
+          <t>Reliability phản ánh khả năng đảm bảo hệ thống vận hành ổn định sau khi thay đổi.
+Collaboration đánh giá:
+- Chia sẻ tri thức
+- Code Review
+- Hỗ trợ đồng đội
+- Phối hợp liên nhóm
+- Khả năng tạo ảnh hưởng tích cực</t>
+        </is>
+      </c>
+      <c r="F15" s="379" t="inlineStr">
+        <is>
+          <t>Cá nhân + Manager đánh giá</t>
+        </is>
+      </c>
+      <c r="G15" s="380" t="n"/>
+      <c r="H15" s="381" t="n"/>
+      <c r="I15" s="381" t="n"/>
+      <c r="J15" s="381" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="382" t="n">
+        <v>10</v>
+      </c>
+      <c r="L15" s="382" t="n"/>
+      <c r="M15" s="381" t="n"/>
+      <c r="N15" s="381" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="O15" s="378" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P15" s="319" t="n"/>
+      <c r="Q15" s="319" t="n"/>
+      <c r="R15" s="319" t="n"/>
+      <c r="S15" s="319" t="n"/>
+    </row>
+    <row r="16" ht="121.5" customHeight="1">
+      <c r="A16" s="332" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="361" t="inlineStr">
+        <is>
+          <t>Collaboration KPI</t>
+        </is>
+      </c>
+      <c r="C16" s="377" t="n"/>
+      <c r="D16" s="378" t="n"/>
+      <c r="E16" s="336" t="inlineStr">
+        <is>
+          <t>Collaboration phản ánh khả năng phối hợp để nâng cao hiệu quả của Team, không phải khả năng giao tiếp đơn thuần.
+Collaboration đánh giá:
+- Chia sẻ tri thức
+- Code Review
+- Hỗ trợ đồng đội
+- Phối hợp liên nhóm
+- Khả năng tạo ảnh hưởng tích cực</t>
+        </is>
+      </c>
+      <c r="F16" s="379" t="inlineStr">
+        <is>
+          <t>Tự đánh giá</t>
+        </is>
+      </c>
+      <c r="G16" s="380" t="n"/>
+      <c r="H16" s="381" t="n"/>
+      <c r="I16" s="381" t="n"/>
+      <c r="J16" s="381" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="382" t="n">
+        <v>10</v>
+      </c>
+      <c r="L16" s="382" t="n"/>
+      <c r="M16" s="381" t="n"/>
+      <c r="N16" s="381" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O16" s="378" t="n">
+        <v>9</v>
+      </c>
+      <c r="P16" s="319" t="n"/>
+      <c r="Q16" s="319" t="n"/>
+      <c r="R16" s="319" t="n"/>
+      <c r="S16" s="319" t="n"/>
+    </row>
+    <row r="17" ht="183" customHeight="1">
+      <c r="A17" s="332" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="361" t="inlineStr">
+        <is>
+          <t>Growth KPI</t>
+        </is>
+      </c>
+      <c r="C17" s="377" t="n"/>
+      <c r="D17" s="378" t="n"/>
+      <c r="E17" s="383" t="inlineStr">
+        <is>
+          <t>Growth phản ánh sự phát triển năng lực của cá nhân và khả năng đóng góp vào sự phát triển năng lực của tổ chức.
+Growth không đánh giá:
+- Số giờ học
+- Số chứng chỉ
+- Số khóa học tham gia
+Growth đánh giá:
+- Mức độ phát triển kỹ năng
+- Áp dụng kiến thức vào công việc
+- Đóng góp cải tiến
+- Khả năng phát triển người khác</t>
+        </is>
+      </c>
+      <c r="F17" s="384" t="inlineStr">
+        <is>
+          <t>Tự đánh giá</t>
+        </is>
+      </c>
+      <c r="G17" s="385" t="n"/>
+      <c r="H17" s="386" t="n"/>
+      <c r="I17" s="386" t="n"/>
+      <c r="J17" s="386" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="387" t="n">
+        <v>10</v>
+      </c>
+      <c r="L17" s="387" t="n"/>
+      <c r="M17" s="381" t="n"/>
+      <c r="N17" s="381" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O17" s="378" t="n">
+        <v>8</v>
+      </c>
+      <c r="P17" s="319" t="n"/>
+      <c r="Q17" s="319" t="n"/>
+      <c r="R17" s="319" t="n"/>
+      <c r="S17" s="319" t="n"/>
+    </row>
+    <row r="18" ht="290.25" customHeight="1">
+      <c r="A18" s="332" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" s="361" t="inlineStr">
+        <is>
+          <t>Impact Bonus</t>
+        </is>
+      </c>
+      <c r="C18" s="377" t="n"/>
+      <c r="D18" s="378" t="n"/>
+      <c r="E18" s="383" t="inlineStr">
+        <is>
+          <t>Ghi nhận các giá trị phát sinh ngoài kế hoạch. 
+Ví dụ cho dev:
+- phát hiện bug nghiêm trọng trước khi release
+- nghĩ ra giải pháp giúp giảm 70% thời gian build
+- cứu production lúc nửa đêm
+- viết framework dùng chung cho toàn công ty
+Để tránh cảm tính, mỗi đóng góp nên đáp ứng đủ các tiêu chí:
+- Không nằm trong kế hoạch KPI ban đầu.
+- Có bằng chứng rõ ràng (PR, RFC, tài liệu, RCA, dashboard, số liệu...).
+- Được quản lý hoặc hội đồng xác nhận.
+- Tạo ra giá trị đo được hoặc tác động rõ ràng.</t>
+        </is>
+      </c>
+      <c r="F18" s="388" t="inlineStr">
+        <is>
+          <t>Công thức:
+- 0%: Không có đóng góp
+- 25%: Đóng góp tạo giá trị cho bản thân hoặc một hạng mục nhỏ. Ví dụ: automation cá nhân, phát hiện bug quan trọng, cải tiến workflow cá nhân.
+- 50%: Đóng góp mang lại lợi ích cho cả team. Ví dụ: xây reusable component, tối ưu CI/CD của team, cải thiện coding guideline, mentoring hiệu quả.
+- 75%: Đóng góp được nhiều team sử dụng hoặc tạo ảnh hưởng liên phòng ban. Ví dụ: xây internal library, framework dùng chung, xử lý production incident lớn, đào tạo nhiều team.
+- 100%: Đóng góp tạo ảnh hưởng rõ rệt tới toàn bộ Engineering hoặc doanh nghiệp. Ví dụ: nền tảng mới giúp giảm đáng kể chi phí/vận hành, sáng kiến được triển khai toàn công ty, giải pháp tạo lợi thế cạnh tranh hoặc doanh thu.</t>
+        </is>
+      </c>
+      <c r="G18" s="385" t="n"/>
+      <c r="H18" s="386" t="n"/>
+      <c r="I18" s="386" t="n"/>
+      <c r="J18" s="386" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K18" s="387" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="387" t="n"/>
+      <c r="M18" s="381" t="n"/>
+      <c r="N18" s="381" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O18" s="378" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="319" t="n"/>
+      <c r="Q18" s="319" t="n"/>
+      <c r="R18" s="319" t="n"/>
+      <c r="S18" s="319" t="n"/>
+    </row>
+    <row r="19" ht="30.75" customHeight="1">
+      <c r="A19" s="343" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="B19" s="369" t="inlineStr">
+        <is>
+          <t>Innovation (tạo ra giá trị mới)</t>
+        </is>
+      </c>
+      <c r="C19" s="370" t="n"/>
+      <c r="D19" s="346" t="n"/>
+      <c r="E19" s="375" t="inlineStr">
+        <is>
+          <t>Tạo ra giá trị mới cho công ty.
+Ví dụ: Viết script giúp giảm 6 giờ release xuống còn 20 phút.</t>
+        </is>
+      </c>
+      <c r="F19" s="389" t="n"/>
+      <c r="G19" s="389" t="n"/>
+      <c r="H19" s="349" t="n"/>
+      <c r="I19" s="349" t="n"/>
+      <c r="J19" s="349" t="n"/>
+      <c r="K19" s="372" t="n"/>
+      <c r="L19" s="349" t="n"/>
+      <c r="M19" s="349" t="n"/>
+      <c r="N19" s="351" t="n"/>
+      <c r="O19" s="376" t="n"/>
+      <c r="P19" s="319" t="n"/>
+      <c r="Q19" s="319" t="n"/>
+      <c r="R19" s="319" t="n"/>
+      <c r="S19" s="319" t="n"/>
+    </row>
+    <row r="20" ht="76.5" customHeight="1">
+      <c r="A20" s="343" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="B20" s="369" t="inlineStr">
+        <is>
+          <t>Exceptional Contribution</t>
+        </is>
+      </c>
+      <c r="C20" s="370" t="n"/>
+      <c r="D20" s="346" t="n"/>
+      <c r="E20" s="375" t="inlineStr">
+        <is>
+          <t>Làm vượt kỳ vọng.
+Ví dụ:
+- hoàn thành dự án trước deadline lớn
+- hỗ trợ nhiều team
+- xử lý workload đột biến</t>
+        </is>
+      </c>
+      <c r="F20" s="390" t="n"/>
+      <c r="G20" s="390" t="n"/>
+      <c r="H20" s="349" t="n"/>
+      <c r="I20" s="349" t="n"/>
+      <c r="J20" s="349" t="n"/>
+      <c r="K20" s="372" t="n"/>
+      <c r="L20" s="349" t="n"/>
+      <c r="M20" s="349" t="n"/>
+      <c r="N20" s="351" t="n"/>
+      <c r="O20" s="376" t="n"/>
+      <c r="P20" s="319" t="n"/>
+      <c r="Q20" s="319" t="n"/>
+      <c r="R20" s="319" t="n"/>
+      <c r="S20" s="319" t="n"/>
+    </row>
+    <row r="21" ht="91.5" customHeight="1">
+      <c r="A21" s="343" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="B21" s="369" t="inlineStr">
+        <is>
+          <t>Organization Impact</t>
+        </is>
+      </c>
+      <c r="C21" s="370" t="n"/>
+      <c r="D21" s="346" t="n"/>
+      <c r="E21" s="375" t="inlineStr">
+        <is>
+          <t>Ảnh hưởng ở cấp tổ chức.
+Ví dụ: 
+- xây Coding Standard
+- tạo Handbook
+- đào tạo nội bộ (workshop)
+- mentoring nhiều team</t>
+        </is>
+      </c>
+      <c r="F21" s="390" t="n"/>
+      <c r="G21" s="390" t="n"/>
+      <c r="H21" s="349" t="n"/>
+      <c r="I21" s="349" t="n"/>
+      <c r="J21" s="349" t="n"/>
+      <c r="K21" s="372" t="n"/>
+      <c r="L21" s="349" t="n"/>
+      <c r="M21" s="349" t="n"/>
+      <c r="N21" s="351" t="n"/>
+      <c r="O21" s="376" t="n"/>
+      <c r="P21" s="319" t="n"/>
+      <c r="Q21" s="319" t="n"/>
+      <c r="R21" s="319" t="n"/>
+      <c r="S21" s="319" t="n"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="343" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="B22" s="369" t="inlineStr">
+        <is>
+          <t>Emergency Response</t>
+        </is>
+      </c>
+      <c r="C22" s="370" t="n"/>
+      <c r="D22" s="346" t="n"/>
+      <c r="E22" s="375" t="inlineStr">
+        <is>
+          <t>Xử lý tình huống khẩn cấp ảnh hưởng tới công ty / tổ chức</t>
+        </is>
+      </c>
+      <c r="F22" s="29" t="n"/>
+      <c r="G22" s="29" t="n"/>
+      <c r="H22" s="349" t="n"/>
+      <c r="I22" s="349" t="n"/>
+      <c r="J22" s="349" t="n"/>
+      <c r="K22" s="372" t="n"/>
+      <c r="L22" s="349" t="n"/>
+      <c r="M22" s="349" t="n"/>
+      <c r="N22" s="351" t="n"/>
+      <c r="O22" s="376" t="n"/>
+      <c r="P22" s="319" t="n"/>
+      <c r="Q22" s="319" t="n"/>
+      <c r="R22" s="319" t="n"/>
+      <c r="S22" s="319" t="n"/>
+    </row>
+    <row r="23" ht="30.75" customHeight="1">
+      <c r="A23" s="391" t="inlineStr">
+        <is>
+          <t>B.</t>
+        </is>
+      </c>
+      <c r="B23" s="392" t="inlineStr">
+        <is>
+          <t>TINH THẦN VÀ TRÁCH NHIỆM (TỶ TRỌNG: 15%)</t>
+        </is>
+      </c>
+      <c r="C23" s="393" t="n"/>
+      <c r="D23" s="394">
+        <f>SUBTOTAL(9,D24:D26)</f>
+        <v/>
+      </c>
+      <c r="E23" s="395" t="n"/>
+      <c r="F23" s="395">
+        <f> Trọng số * Điểm đạt * Tỷ trọng</f>
+        <v/>
+      </c>
+      <c r="G23" s="396" t="n"/>
+      <c r="H23" s="397" t="n"/>
+      <c r="I23" s="397" t="n"/>
+      <c r="J23" s="397" t="n"/>
+      <c r="K23" s="398">
+        <f>SUBTOTAL(9,K24:K26)</f>
+        <v/>
+      </c>
+      <c r="L23" s="399" t="n"/>
+      <c r="M23" s="400" t="n"/>
+      <c r="N23" s="401" t="n"/>
+      <c r="O23" s="402">
+        <f>SUBTOTAL(9,O24:O26)</f>
+        <v/>
+      </c>
+      <c r="P23" s="403" t="n"/>
+      <c r="Q23" s="404" t="n"/>
+      <c r="R23" s="405" t="n"/>
+      <c r="S23" s="406" t="n"/>
+      <c r="T23" s="406" t="n"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="407" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" s="408" t="inlineStr">
+        <is>
+          <t>Chủ động trong công việc</t>
+        </is>
+      </c>
+      <c r="C24" s="359" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" s="409" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E24" s="410" t="inlineStr">
+        <is>
+          <t>Theo bảng tiêu chí B, C</t>
+        </is>
+      </c>
+      <c r="F24" s="411" t="n"/>
+      <c r="G24" s="411" t="n"/>
+      <c r="H24" s="412" t="n">
+        <v>10</v>
+      </c>
+      <c r="I24" s="413">
+        <f>H24/C24</f>
+        <v/>
+      </c>
+      <c r="J24" s="414" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K24" s="414">
+        <f>$D24*$I24*15%</f>
+        <v/>
+      </c>
+      <c r="L24" s="415" t="n">
+        <v>9</v>
+      </c>
+      <c r="M24" s="416">
+        <f>L24/C24</f>
+        <v/>
+      </c>
+      <c r="N24" s="359" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O24" s="417">
+        <f>$D24*$M24*15%</f>
+        <v/>
+      </c>
+      <c r="P24" s="403" t="n"/>
+      <c r="Q24" s="418" t="n"/>
+      <c r="R24" s="419" t="n"/>
+      <c r="S24" s="419" t="n"/>
+      <c r="T24" s="419" t="n"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="407" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="408" t="inlineStr">
+        <is>
+          <t>Phối hợp trong công việc</t>
+        </is>
+      </c>
+      <c r="C25" s="359" t="n">
+        <v>10</v>
+      </c>
+      <c r="D25" s="409" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F25" s="411" t="n"/>
+      <c r="G25" s="411" t="n"/>
+      <c r="H25" s="412" t="n">
+        <v>10</v>
+      </c>
+      <c r="I25" s="413">
+        <f>H25/C25</f>
+        <v/>
+      </c>
+      <c r="J25" s="414" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K25" s="414">
+        <f>$D25*$I25*15%</f>
+        <v/>
+      </c>
+      <c r="L25" s="389" t="n">
+        <v>8</v>
+      </c>
+      <c r="M25" s="416">
+        <f>L25/C25</f>
+        <v/>
+      </c>
+      <c r="N25" s="359" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O25" s="417">
+        <f>$D25*$M25*15%</f>
+        <v/>
+      </c>
+      <c r="P25" s="403" t="n"/>
+      <c r="Q25" s="418" t="n"/>
+      <c r="R25" s="419" t="n"/>
+      <c r="S25" s="419" t="n"/>
+      <c r="T25" s="419" t="n"/>
+    </row>
+    <row r="26" ht="45.75" customHeight="1">
+      <c r="A26" s="407" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="408" t="inlineStr">
+        <is>
+          <t>Tuân thủ kỷ luật trong công việc, chấp hành yêu cầu cấp trên và các quy định nội quy của Công ty</t>
+        </is>
+      </c>
+      <c r="C26" s="359" t="n">
+        <v>10</v>
+      </c>
+      <c r="D26" s="409" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E26" s="420" t="n"/>
+      <c r="F26" s="411" t="n"/>
+      <c r="G26" s="411" t="n"/>
+      <c r="H26" s="412" t="n">
+        <v>10</v>
+      </c>
+      <c r="I26" s="413">
+        <f>H26/C26</f>
+        <v/>
+      </c>
+      <c r="J26" s="414" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K26" s="414">
+        <f>$D26*$I26*15%</f>
+        <v/>
+      </c>
+      <c r="L26" s="389" t="n">
+        <v>10</v>
+      </c>
+      <c r="M26" s="416">
+        <f>L26/C26</f>
+        <v/>
+      </c>
+      <c r="N26" s="359" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O26" s="417">
+        <f>$D26*$M26*15%</f>
+        <v/>
+      </c>
+      <c r="P26" s="403" t="n"/>
+      <c r="Q26" s="418" t="n"/>
+      <c r="R26" s="419" t="n"/>
+      <c r="S26" s="419" t="n"/>
+      <c r="T26" s="419" t="n"/>
+    </row>
+    <row r="27" ht="30.75" customHeight="1">
+      <c r="A27" s="391" t="inlineStr">
+        <is>
+          <t>C.</t>
+        </is>
+      </c>
+      <c r="B27" s="327" t="inlineStr">
+        <is>
+          <t>KỶ LUẬT LAO ĐỘNG (TỶ TRỌNG: 5%)</t>
+        </is>
+      </c>
+      <c r="C27" s="421" t="n"/>
+      <c r="D27" s="422">
+        <f>SUBTOTAL(9,D28:D31)</f>
+        <v/>
+      </c>
+      <c r="E27" s="423" t="n"/>
+      <c r="F27" s="395">
+        <f> Trọng số * Điểm đạt * Tỷ trọng</f>
+        <v/>
+      </c>
+      <c r="G27" s="424" t="n"/>
+      <c r="H27" s="425" t="n"/>
+      <c r="I27" s="425" t="n"/>
+      <c r="J27" s="425" t="n"/>
+      <c r="K27" s="426">
+        <f>SUBTOTAL(9,K28:K31)</f>
+        <v/>
+      </c>
+      <c r="L27" s="427" t="n"/>
+      <c r="M27" s="428" t="n"/>
+      <c r="N27" s="427" t="n"/>
+      <c r="O27" s="429">
+        <f>SUBTOTAL(9,O28:O31)</f>
+        <v/>
+      </c>
+      <c r="P27" s="403" t="n"/>
+      <c r="Q27" s="404" t="n"/>
+      <c r="R27" s="405" t="n"/>
+      <c r="S27" s="405" t="n"/>
+      <c r="T27" s="405" t="n"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="407" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="408" t="inlineStr">
+        <is>
+          <t>Đi muộn, về sớm</t>
+        </is>
+      </c>
+      <c r="C28" s="359" t="n">
+        <v>10</v>
+      </c>
+      <c r="D28" s="409" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E28" s="430" t="inlineStr">
+        <is>
+          <t>Theo bảng tiêu chí B, C</t>
+        </is>
+      </c>
+      <c r="F28" s="411" t="n"/>
+      <c r="G28" s="411" t="n"/>
+      <c r="H28" s="412" t="n">
+        <v>10</v>
+      </c>
+      <c r="I28" s="413">
+        <f>H28/C28</f>
+        <v/>
+      </c>
+      <c r="J28" s="414" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K28" s="431">
+        <f>$D28*$I28*5%</f>
+        <v/>
+      </c>
+      <c r="L28" s="359" t="n">
+        <v>7</v>
+      </c>
+      <c r="M28" s="432">
+        <f>L28/C28</f>
+        <v/>
+      </c>
+      <c r="N28" s="359" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O28" s="433">
+        <f>$D28*$M28*5%</f>
+        <v/>
+      </c>
+      <c r="P28" s="403" t="n"/>
+      <c r="Q28" s="418" t="n"/>
+      <c r="R28" s="419" t="n"/>
+      <c r="S28" s="419" t="n"/>
+      <c r="T28" s="419" t="n"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="407" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="408" t="inlineStr">
+        <is>
+          <t>Nghỉ không phép</t>
+        </is>
+      </c>
+      <c r="C29" s="359" t="n">
+        <v>10</v>
+      </c>
+      <c r="D29" s="409" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F29" s="411" t="n"/>
+      <c r="G29" s="411" t="n"/>
+      <c r="H29" s="412" t="n">
+        <v>10</v>
+      </c>
+      <c r="I29" s="413">
+        <f>H29/C29</f>
+        <v/>
+      </c>
+      <c r="J29" s="414" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K29" s="431">
+        <f>$D29*$I29*5%</f>
+        <v/>
+      </c>
+      <c r="L29" s="359" t="n">
+        <v>7</v>
+      </c>
+      <c r="M29" s="432">
+        <f>L29/C29</f>
+        <v/>
+      </c>
+      <c r="N29" s="359" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O29" s="433">
+        <f>$D29*$M29*5%</f>
+        <v/>
+      </c>
+      <c r="P29" s="403" t="n"/>
+      <c r="Q29" s="418" t="n"/>
+      <c r="R29" s="419" t="n"/>
+      <c r="S29" s="419" t="n"/>
+      <c r="T29" s="419" t="n"/>
+    </row>
+    <row r="30" ht="30.75" customHeight="1">
+      <c r="A30" s="407" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="408" t="inlineStr">
+        <is>
+          <t>Quên không chấm công (check in và check out)</t>
+        </is>
+      </c>
+      <c r="C30" s="359" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" s="409" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F30" s="411" t="n"/>
+      <c r="G30" s="411" t="n"/>
+      <c r="H30" s="412" t="n">
+        <v>10</v>
+      </c>
+      <c r="I30" s="413">
+        <f>H30/C30</f>
+        <v/>
+      </c>
+      <c r="J30" s="414" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K30" s="431">
+        <f>$D30*$I30*5%</f>
+        <v/>
+      </c>
+      <c r="L30" s="359" t="n">
+        <v>6</v>
+      </c>
+      <c r="M30" s="432">
+        <f>L30/C30</f>
+        <v/>
+      </c>
+      <c r="N30" s="359" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O30" s="433">
+        <f>$D30*$M30*5%</f>
+        <v/>
+      </c>
+      <c r="P30" s="403" t="n"/>
+      <c r="Q30" s="418" t="n"/>
+      <c r="R30" s="419" t="n"/>
+      <c r="S30" s="419" t="n"/>
+      <c r="T30" s="419" t="n"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="434" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="435" t="inlineStr">
+        <is>
+          <t>Xanh-Sạch-Đẹp</t>
+        </is>
+      </c>
+      <c r="C31" s="359" t="n">
+        <v>10</v>
+      </c>
+      <c r="D31" s="409" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E31" s="62" t="n"/>
+      <c r="F31" s="411" t="n"/>
+      <c r="G31" s="411" t="n"/>
+      <c r="H31" s="412" t="n">
+        <v>10</v>
+      </c>
+      <c r="I31" s="413">
+        <f>H31/C31</f>
+        <v/>
+      </c>
+      <c r="J31" s="414" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K31" s="431">
+        <f>$D31*$I31*5%</f>
+        <v/>
+      </c>
+      <c r="L31" s="359" t="n">
+        <v>6</v>
+      </c>
+      <c r="M31" s="432">
+        <f>L31/C31</f>
+        <v/>
+      </c>
+      <c r="N31" s="359" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O31" s="433">
+        <f>$D31*$M31*5%</f>
+        <v/>
+      </c>
+      <c r="P31" s="403" t="n"/>
+      <c r="Q31" s="418" t="n"/>
+      <c r="R31" s="419" t="n"/>
+      <c r="S31" s="419" t="n"/>
+      <c r="T31" s="419" t="n"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="436" t="inlineStr">
+        <is>
+          <t>TỔNG</t>
+        </is>
+      </c>
+      <c r="B32" s="127" t="n"/>
+      <c r="C32" s="27" t="n"/>
+      <c r="D32" s="437" t="n"/>
+      <c r="E32" s="438" t="n"/>
+      <c r="F32" s="437" t="n"/>
+      <c r="G32" s="437" t="n"/>
+      <c r="H32" s="437" t="n"/>
+      <c r="I32" s="437" t="n"/>
+      <c r="J32" s="437" t="n"/>
+      <c r="K32" s="439">
+        <f>SUM(K27,K23,K3)</f>
+        <v/>
+      </c>
+      <c r="L32" s="439" t="n"/>
+      <c r="M32" s="440" t="n"/>
+      <c r="N32" s="440" t="n"/>
+      <c r="O32" s="439">
+        <f>SUM(O27,O23,O3)</f>
+        <v/>
+      </c>
+      <c r="P32" s="403" t="n"/>
+      <c r="Q32" s="441" t="n"/>
+      <c r="R32" s="442" t="n"/>
+      <c r="S32" s="442" t="n"/>
+      <c r="T32" s="443" t="n"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="444" t="inlineStr">
+        <is>
+          <t>TỔNG CỘNG= ((Nhân viên đánh giá *1)+(CBQL đánh giá *2))/3</t>
+        </is>
+      </c>
+      <c r="B33" s="445" t="n"/>
+      <c r="C33" s="446" t="n"/>
+      <c r="D33" s="446" t="n"/>
+      <c r="E33" s="446" t="n"/>
+      <c r="F33" s="446" t="n"/>
+      <c r="G33" s="446" t="n"/>
+      <c r="H33" s="447">
+        <f>(K32 + O32*2)/3</f>
+        <v/>
+      </c>
+      <c r="I33" s="127" t="n"/>
+      <c r="J33" s="127" t="n"/>
+      <c r="K33" s="127" t="n"/>
+      <c r="L33" s="127" t="n"/>
+      <c r="M33" s="127" t="n"/>
+      <c r="N33" s="127" t="n"/>
+      <c r="O33" s="27" t="n"/>
+      <c r="P33" s="448" t="n"/>
+      <c r="Q33" s="448" t="n"/>
+      <c r="R33" s="448" t="n"/>
+      <c r="S33" s="448" t="n"/>
+      <c r="T33" s="449" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="H33:O33"/>
+    <mergeCell ref="E28:E31"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G19:G22"/>
+    <mergeCell ref="H1:K1"/>
+    <mergeCell ref="L1:O1"/>
+    <mergeCell ref="F19:F22"/>
+    <mergeCell ref="A1:A2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -8477,7 +11575,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -10016,100 +13114,99 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FFFFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A2:F21"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.142857142857141" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="9.142857142857141" customWidth="1" style="21" min="1" max="1"/>
-    <col width="28.8571428571429" customWidth="1" style="21" min="2" max="2"/>
-    <col width="48.2857142857143" customWidth="1" style="21" min="3" max="4"/>
-    <col width="68.4285714285714" customWidth="1" style="21" min="5" max="5"/>
-    <col width="33" customWidth="1" style="21" min="6" max="6"/>
-    <col width="9.142857142857141" customWidth="1" style="21" min="7" max="16384"/>
+    <col width="9.140625" customWidth="1" min="1" max="1"/>
+    <col width="28.85546875" customWidth="1" min="2" max="2"/>
+    <col width="48.28515625" customWidth="1" min="3" max="3"/>
+    <col width="68.42578125" customWidth="1" min="5" max="5"/>
+    <col width="33" customWidth="1" min="6" max="6"/>
+    <col width="9.140625" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="2" ht="18.6" customHeight="1">
-      <c r="A2" s="40" t="inlineStr">
+      <c r="A2" s="450" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B2" s="40" t="inlineStr">
+      <c r="B2" s="450" t="inlineStr">
         <is>
           <t>Tiêu chí</t>
         </is>
       </c>
-      <c r="C2" s="40" t="inlineStr">
+      <c r="C2" s="450" t="inlineStr">
         <is>
           <t>Mô tả</t>
         </is>
       </c>
-      <c r="D2" s="40" t="inlineStr">
+      <c r="D2" s="450" t="inlineStr">
         <is>
           <t>Chi tiết</t>
         </is>
       </c>
-      <c r="E2" s="40" t="inlineStr">
+      <c r="E2" s="450" t="inlineStr">
         <is>
           <t>Công thức tính</t>
         </is>
       </c>
-      <c r="F2" s="41" t="inlineStr">
+      <c r="F2" s="451" t="inlineStr">
         <is>
           <t>Thang điểm</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="42" t="inlineStr">
+    <row r="3" ht="41.25" customHeight="1">
+      <c r="A3" s="452" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B3" s="43" t="inlineStr">
+      <c r="B3" s="453" t="inlineStr">
         <is>
           <t>Hiệu quả công việc</t>
         </is>
       </c>
-      <c r="C3" s="43" t="n"/>
-      <c r="D3" s="43" t="n"/>
-      <c r="E3" s="44" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> = 30% * Delivery + 20% * Quality + 10% * Reliability + 10 * Collaboration + 5% * Growth</t>
-        </is>
-      </c>
-      <c r="F3" s="43" t="n"/>
+      <c r="C3" s="453" t="n"/>
+      <c r="D3" s="453" t="n"/>
+      <c r="E3" s="454" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> = 35% * Delivery + 20% * Quality + 10% * Reliability + 10% * Collaboration + 5% * Growth + 20% * Impact Bonus</t>
+        </is>
+      </c>
+      <c r="F3" s="453" t="n"/>
     </row>
     <row r="4" ht="46.5" customHeight="1">
-      <c r="A4" s="45" t="n">
+      <c r="A4" s="455" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="455" t="inlineStr">
         <is>
           <t>Delivery KPI</t>
         </is>
       </c>
-      <c r="C4" s="46" t="inlineStr">
+      <c r="C4" s="456" t="inlineStr">
         <is>
           <t>Delivery phản ánh khả năng chuyển giao công việc đã cam kết thành kết quả có giá trị.</t>
         </is>
       </c>
-      <c r="D4" s="47" t="n"/>
-      <c r="E4" s="47" t="inlineStr">
+      <c r="D4" s="457" t="n"/>
+      <c r="E4" s="457" t="inlineStr">
         <is>
           <t xml:space="preserve"> = 40% × Commitment Achievement + 25% × Schedule Performance + 20% × Work Throughput + 15% × Delivery Ownership</t>
         </is>
       </c>
-      <c r="F4" s="47" t="n"/>
+      <c r="F4" s="457" t="n"/>
     </row>
     <row r="5" ht="131.25" customHeight="1">
-      <c r="A5" s="48" t="n"/>
+      <c r="A5" s="458" t="n"/>
       <c r="B5" s="49" t="inlineStr">
         <is>
           <t>Commitment Achievement</t>
@@ -10120,7 +13217,7 @@
           <t>Hoàn thành công việc đã cam kết</t>
         </is>
       </c>
-      <c r="D5" s="50" t="inlineStr">
+      <c r="D5" s="459" t="inlineStr">
         <is>
           <t>Đánh giá khả năng hoàn thành các Jira Task/Ticket đã cam kết.
 Không tính:
@@ -10130,12 +13227,12 @@
 - Blocker ngoài khả năng kiểm soát</t>
         </is>
       </c>
-      <c r="E5" s="48" t="inlineStr">
+      <c r="E5" s="458" t="inlineStr">
         <is>
           <t>Commitment Achievement = Completed Scope / Committed Scope</t>
         </is>
       </c>
-      <c r="F5" s="48" t="inlineStr">
+      <c r="F5" s="458" t="inlineStr">
         <is>
           <t>Tỷ lệ hoàn thành	Điểm
 ≥100%	100
@@ -10147,7 +13244,7 @@
       </c>
     </row>
     <row r="6" ht="132" customHeight="1">
-      <c r="A6" s="48" t="n"/>
+      <c r="A6" s="458" t="n"/>
       <c r="B6" s="49" t="inlineStr">
         <is>
           <t>Schedule Performance</t>
@@ -10158,7 +13255,7 @@
           <t>Hoàn thành đúng thời hạn</t>
         </is>
       </c>
-      <c r="D6" s="50" t="inlineStr">
+      <c r="D6" s="459" t="inlineStr">
         <is>
           <t>Đánh giá mức độ hoàn thành đúng thời hạn.
 Không tính:
@@ -10167,12 +13264,12 @@
 - Delay do phụ thuộc team khác</t>
         </is>
       </c>
-      <c r="E6" s="48" t="inlineStr">
+      <c r="E6" s="458" t="inlineStr">
         <is>
           <t>Schedule Performance = On-time Completed / Completed Issues</t>
         </is>
       </c>
-      <c r="F6" s="48" t="inlineStr">
+      <c r="F6" s="458" t="inlineStr">
         <is>
           <t>On-time Rate	Điểm
 ≥95%	100
@@ -10184,7 +13281,7 @@
       </c>
     </row>
     <row r="7" ht="132" customHeight="1">
-      <c r="A7" s="48" t="n"/>
+      <c r="A7" s="458" t="n"/>
       <c r="B7" s="49" t="inlineStr">
         <is>
           <t>Work Throughput</t>
@@ -10195,7 +13292,7 @@
           <t>Khối lượng công việc hoàn thành theo Scope Score</t>
         </is>
       </c>
-      <c r="D7" s="50" t="inlineStr">
+      <c r="D7" s="459" t="inlineStr">
         <is>
           <t>Đánh giá công việc hoàn thành dựa trên level/ cấp bậc nhân sự
 Notes: 
@@ -10203,8 +13300,8 @@
 - Đề xuất sử dụng Scope Score.</t>
         </is>
       </c>
-      <c r="E7" s="48" t="n"/>
-      <c r="F7" s="48" t="inlineStr">
+      <c r="E7" s="458" t="n"/>
+      <c r="F7" s="458" t="inlineStr">
         <is>
           <t>Throughput	Điểm
 ≥95%	100
@@ -10215,7 +13312,7 @@
       </c>
     </row>
     <row r="8" ht="195" customHeight="1">
-      <c r="A8" s="51" t="n"/>
+      <c r="A8" s="460" t="n"/>
       <c r="B8" s="52" t="inlineStr">
         <is>
           <t>Delivery Ownership</t>
@@ -10226,14 +13323,14 @@
           <t>Chủ động xử lý và đảm bảo tiến độ</t>
         </is>
       </c>
-      <c r="D8" s="51" t="inlineStr">
+      <c r="D8" s="460" t="inlineStr">
         <is>
           <t xml:space="preserve">Đánh giá mức độ chủ động trong quá trình thực hiện.
 </t>
         </is>
       </c>
-      <c r="E8" s="51" t="n"/>
-      <c r="F8" s="51" t="inlineStr">
+      <c r="E8" s="460" t="n"/>
+      <c r="F8" s="460" t="inlineStr">
         <is>
           <t>Manager đánh giá theo Rubric.
 Mức	Tiêu chí
@@ -10246,42 +13343,42 @@
       </c>
     </row>
     <row r="9" ht="44.45" customHeight="1">
-      <c r="A9" s="53" t="n">
+      <c r="A9" s="461" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="53" t="inlineStr">
+      <c r="B9" s="461" t="inlineStr">
         <is>
           <t>Quality KPI</t>
         </is>
       </c>
-      <c r="C9" s="54" t="inlineStr">
+      <c r="C9" s="462" t="inlineStr">
         <is>
           <t>Quality phản ánh khả năng tạo ra phần mềm đáp ứng yêu cầu chất lượng trong toàn bộ SDLC, không chỉ là số lượng bug sau khi release.</t>
         </is>
       </c>
-      <c r="D9" s="55" t="n"/>
-      <c r="E9" s="55" t="inlineStr">
+      <c r="D9" s="463" t="n"/>
+      <c r="E9" s="463" t="inlineStr">
         <is>
           <t>Quality Score = 25% × Code Quality + 20% × Testing Quality + 15% × Build &amp; Release Quality + 25% × Production Quality + 15% × Quality Process Compliance</t>
         </is>
       </c>
-      <c r="F9" s="55" t="n"/>
+      <c r="F9" s="463" t="n"/>
     </row>
     <row r="10" ht="101.45" customHeight="1">
-      <c r="A10" s="48" t="n"/>
-      <c r="B10" s="48" t="inlineStr">
+      <c r="A10" s="458" t="n"/>
+      <c r="B10" s="458" t="inlineStr">
         <is>
           <t>Code Quality</t>
         </is>
       </c>
-      <c r="C10" s="56" t="inlineStr">
+      <c r="C10" s="464" t="inlineStr">
         <is>
           <t>Đánh giá chất lượng mã nguồn trước khi merge.</t>
         </is>
       </c>
-      <c r="D10" s="48" t="n"/>
-      <c r="E10" s="48" t="n"/>
-      <c r="F10" s="48" t="inlineStr">
+      <c r="D10" s="458" t="n"/>
+      <c r="E10" s="458" t="n"/>
+      <c r="F10" s="458" t="inlineStr">
         <is>
           <t xml:space="preserve">Điểm	Đánh giá
 95–100	Xuất sắc
@@ -10294,18 +13391,18 @@
       </c>
     </row>
     <row r="11" ht="87" customHeight="1">
-      <c r="A11" s="48" t="n"/>
-      <c r="B11" s="48" t="inlineStr">
+      <c r="A11" s="458" t="n"/>
+      <c r="B11" s="458" t="inlineStr">
         <is>
           <t>Testing Quality</t>
         </is>
       </c>
-      <c r="C11" s="48" t="inlineStr">
+      <c r="C11" s="458" t="inlineStr">
         <is>
           <t>Đánh giá chất lượng kiểm thử (seft test)</t>
         </is>
       </c>
-      <c r="D11" s="48" t="inlineStr">
+      <c r="D11" s="458" t="inlineStr">
         <is>
           <t>Tham số đầu vào
 - Unit Test Coverage
@@ -10315,22 +13412,22 @@
 - Flaky Test</t>
         </is>
       </c>
-      <c r="E11" s="48" t="n"/>
-      <c r="F11" s="48" t="n"/>
+      <c r="E11" s="458" t="n"/>
+      <c r="F11" s="458" t="n"/>
     </row>
     <row r="12" ht="87" customHeight="1">
-      <c r="A12" s="48" t="n"/>
-      <c r="B12" s="48" t="inlineStr">
+      <c r="A12" s="458" t="n"/>
+      <c r="B12" s="458" t="inlineStr">
         <is>
           <t xml:space="preserve">Build &amp; Release Quality </t>
         </is>
       </c>
-      <c r="C12" s="48" t="inlineStr">
+      <c r="C12" s="458" t="inlineStr">
         <is>
           <t>Đánh giá chất lượng build.</t>
         </is>
       </c>
-      <c r="D12" s="48" t="inlineStr">
+      <c r="D12" s="458" t="inlineStr">
         <is>
           <t>Tham số:
 - Build Success Rate
@@ -10339,8 +13436,8 @@
 - Release Checklist</t>
         </is>
       </c>
-      <c r="E12" s="48" t="n"/>
-      <c r="F12" s="48" t="inlineStr">
+      <c r="E12" s="458" t="n"/>
+      <c r="F12" s="458" t="inlineStr">
         <is>
           <t xml:space="preserve">Điều kiện	Điểm
 Không lỗi build, không rollback	100
@@ -10352,18 +13449,18 @@
       </c>
     </row>
     <row r="13" ht="101.45" customHeight="1">
-      <c r="A13" s="48" t="n"/>
-      <c r="B13" s="48" t="inlineStr">
+      <c r="A13" s="458" t="n"/>
+      <c r="B13" s="458" t="inlineStr">
         <is>
           <t>Production Quality</t>
         </is>
       </c>
-      <c r="C13" s="48" t="inlineStr">
+      <c r="C13" s="458" t="inlineStr">
         <is>
           <t>Đây là nhóm phản ánh Outcome của Quality.</t>
         </is>
       </c>
-      <c r="D13" s="48" t="inlineStr">
+      <c r="D13" s="458" t="inlineStr">
         <is>
           <t>Tham số
 - Escaped Defects
@@ -10372,8 +13469,8 @@
 - Customer Complaint</t>
         </is>
       </c>
-      <c r="E13" s="48" t="n"/>
-      <c r="F13" s="48" t="inlineStr">
+      <c r="E13" s="458" t="n"/>
+      <c r="F13" s="458" t="inlineStr">
         <is>
           <t xml:space="preserve">Điều kiện	Điểm
 Không Critical Bug	100
@@ -10386,18 +13483,18 @@
       </c>
     </row>
     <row r="14" ht="101.45" customHeight="1">
-      <c r="A14" s="48" t="n"/>
-      <c r="B14" s="48" t="inlineStr">
+      <c r="A14" s="458" t="n"/>
+      <c r="B14" s="458" t="inlineStr">
         <is>
           <t>Quality Process Compliance</t>
         </is>
       </c>
-      <c r="C14" s="48" t="inlineStr">
+      <c r="C14" s="458" t="inlineStr">
         <is>
           <t>Đánh giá việc tuân thủ Quality Practice.</t>
         </is>
       </c>
-      <c r="D14" s="48" t="inlineStr">
+      <c r="D14" s="458" t="inlineStr">
         <is>
           <t>Pull Request Checklist
 Definition of Done
@@ -10406,8 +13503,8 @@
 Documentation</t>
         </is>
       </c>
-      <c r="E14" s="48" t="n"/>
-      <c r="F14" s="48" t="inlineStr">
+      <c r="E14" s="458" t="n"/>
+      <c r="F14" s="458" t="inlineStr">
         <is>
           <t xml:space="preserve">Mức	Mô tả
 5	Luôn tuân thủ đầy đủ quy trình
@@ -10420,20 +13517,20 @@
       </c>
     </row>
     <row r="15" ht="144.95" customHeight="1">
-      <c r="A15" s="53" t="n">
+      <c r="A15" s="461" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="53" t="inlineStr">
+      <c r="B15" s="461" t="inlineStr">
         <is>
           <t>Reliability KPI</t>
         </is>
       </c>
-      <c r="C15" s="54" t="inlineStr">
+      <c r="C15" s="462" t="inlineStr">
         <is>
           <t>Reliability phản ánh khả năng đảm bảo hệ thống vận hành ổn định sau khi thay đổi.</t>
         </is>
       </c>
-      <c r="D15" s="55" t="inlineStr">
+      <c r="D15" s="463" t="inlineStr">
         <is>
           <t>Reliability không đánh giá:
 - Số lượng Incident được xử lý
@@ -10446,22 +13543,22 @@
 - Khả năng phục hồi khi xảy ra sự cố</t>
         </is>
       </c>
-      <c r="E15" s="55" t="inlineStr">
+      <c r="E15" s="463" t="inlineStr">
         <is>
           <t>Reliability Score = 35% × Change Reliability + 30% × Incident Quality + 20% × Recovery Effectiveness + 15% × Operational Discipline</t>
         </is>
       </c>
-      <c r="F15" s="55" t="n"/>
+      <c r="F15" s="463" t="n"/>
     </row>
     <row r="16" ht="57.95" customHeight="1">
-      <c r="A16" s="48" t="n"/>
-      <c r="B16" s="48" t="inlineStr">
+      <c r="A16" s="458" t="n"/>
+      <c r="B16" s="458" t="inlineStr">
         <is>
           <t>Change Reliability</t>
         </is>
       </c>
-      <c r="C16" s="48" t="n"/>
-      <c r="D16" s="48" t="inlineStr">
+      <c r="C16" s="458" t="n"/>
+      <c r="D16" s="458" t="inlineStr">
         <is>
           <t>Đầu vào:
 - Change Failure Rate
@@ -10469,18 +13566,18 @@
 - Failed Deployment</t>
         </is>
       </c>
-      <c r="E16" s="48" t="n"/>
-      <c r="F16" s="48" t="n"/>
+      <c r="E16" s="458" t="n"/>
+      <c r="F16" s="458" t="n"/>
     </row>
     <row r="17" ht="57.95" customHeight="1">
-      <c r="A17" s="48" t="n"/>
-      <c r="B17" s="48" t="inlineStr">
+      <c r="A17" s="458" t="n"/>
+      <c r="B17" s="458" t="inlineStr">
         <is>
           <t>Incident Quality</t>
         </is>
       </c>
-      <c r="C17" s="48" t="n"/>
-      <c r="D17" s="48" t="inlineStr">
+      <c r="C17" s="458" t="n"/>
+      <c r="D17" s="458" t="inlineStr">
         <is>
           <t>Đầu vào: 
 - Critical Incident
@@ -10488,18 +13585,18 @@
 - Escaped Production Issue</t>
         </is>
       </c>
-      <c r="E17" s="48" t="n"/>
-      <c r="F17" s="48" t="n"/>
+      <c r="E17" s="458" t="n"/>
+      <c r="F17" s="458" t="n"/>
     </row>
     <row r="18" ht="57.95" customHeight="1">
-      <c r="A18" s="48" t="n"/>
-      <c r="B18" s="48" t="inlineStr">
+      <c r="A18" s="458" t="n"/>
+      <c r="B18" s="458" t="inlineStr">
         <is>
           <t>Recovery Effectiveness</t>
         </is>
       </c>
-      <c r="C18" s="48" t="n"/>
-      <c r="D18" s="48" t="inlineStr">
+      <c r="C18" s="458" t="n"/>
+      <c r="D18" s="458" t="inlineStr">
         <is>
           <t>Đầu vào: 
 - MTTR
@@ -10507,18 +13604,18 @@
 - Root Cause Analysis</t>
         </is>
       </c>
-      <c r="E18" s="48" t="n"/>
-      <c r="F18" s="48" t="n"/>
+      <c r="E18" s="458" t="n"/>
+      <c r="F18" s="458" t="n"/>
     </row>
     <row r="19" ht="72.59999999999999" customHeight="1">
-      <c r="A19" s="48" t="n"/>
-      <c r="B19" s="48" t="inlineStr">
+      <c r="A19" s="458" t="n"/>
+      <c r="B19" s="458" t="inlineStr">
         <is>
           <t>Operational Discipline</t>
         </is>
       </c>
-      <c r="C19" s="48" t="n"/>
-      <c r="D19" s="48" t="inlineStr">
+      <c r="C19" s="458" t="n"/>
+      <c r="D19" s="458" t="inlineStr">
         <is>
           <t>Đầu vào: 
 - Monitoring
@@ -10527,24 +13624,24 @@
 - Runbook Compliance</t>
         </is>
       </c>
-      <c r="E19" s="48" t="n"/>
-      <c r="F19" s="48" t="n"/>
+      <c r="E19" s="458" t="n"/>
+      <c r="F19" s="458" t="n"/>
     </row>
     <row r="20" ht="87" customHeight="1">
-      <c r="A20" s="53" t="n">
+      <c r="A20" s="461" t="n">
         <v>4</v>
       </c>
-      <c r="B20" s="53" t="inlineStr">
+      <c r="B20" s="461" t="inlineStr">
         <is>
           <t>Collaboration KPI</t>
         </is>
       </c>
-      <c r="C20" s="54" t="inlineStr">
+      <c r="C20" s="462" t="inlineStr">
         <is>
           <t>Collaboration phản ánh khả năng phối hợp để nâng cao hiệu quả của Team, không phải khả năng giao tiếp đơn thuần.</t>
         </is>
       </c>
-      <c r="D20" s="55" t="inlineStr">
+      <c r="D20" s="463" t="inlineStr">
         <is>
           <t>Collaboration đánh giá:
 - Chia sẻ tri thức
@@ -10554,28 +13651,28 @@
 - Khả năng tạo ảnh hưởng tích cực</t>
         </is>
       </c>
-      <c r="E20" s="55" t="inlineStr">
+      <c r="E20" s="463" t="inlineStr">
         <is>
           <t>Collaboration Score = 30% × Code Review Contribution + 30% × Team Collaboration + 20% × Knowledge Sharing + 20% × Cross-team Collaboration</t>
         </is>
       </c>
-      <c r="F20" s="55" t="n"/>
+      <c r="F20" s="463" t="n"/>
     </row>
     <row r="21" ht="144.95" customHeight="1">
-      <c r="A21" s="53" t="n">
+      <c r="A21" s="461" t="n">
         <v>5</v>
       </c>
-      <c r="B21" s="53" t="inlineStr">
+      <c r="B21" s="461" t="inlineStr">
         <is>
           <t>Growth KPI</t>
         </is>
       </c>
-      <c r="C21" s="54" t="inlineStr">
+      <c r="C21" s="462" t="inlineStr">
         <is>
           <t>Growth phản ánh sự phát triển năng lực của cá nhân và khả năng đóng góp vào sự phát triển năng lực của tổ chức.</t>
         </is>
       </c>
-      <c r="D21" s="57" t="inlineStr">
+      <c r="D21" s="465" t="inlineStr">
         <is>
           <t>Growth không đánh giá:
 - Số giờ học
@@ -10588,19 +13685,19 @@
 - Khả năng phát triển người khác</t>
         </is>
       </c>
-      <c r="E21" s="55" t="inlineStr">
+      <c r="E21" s="463" t="inlineStr">
         <is>
           <t>Growth Score = 35% × Learning Goal Achievement + 25% × Skill Improvement + 25% × Continuous Improvement + 15% × Knowledge Contribution</t>
         </is>
       </c>
-      <c r="F21" s="55" t="n"/>
+      <c r="F21" s="463" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11009,7 +14106,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11428,381 +14525,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F300"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="4"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="4"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Điền 1 mã Jira trên mỗi dòng. Loại kế hoạch: Cam kết | Phát sinh | Ngoài phạm vi</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="313" t="inlineStr">
-        <is>
-          <t>Mã Jira</t>
-        </is>
-      </c>
-      <c r="B2" s="313" t="inlineStr">
-        <is>
-          <t>Tên công việc</t>
-        </is>
-      </c>
-      <c r="C2" s="313" t="inlineStr">
-        <is>
-          <t>Loại kế hoạch</t>
-        </is>
-      </c>
-      <c r="D2" s="313" t="inlineStr">
-        <is>
-          <t>Hạn dự kiến</t>
-        </is>
-      </c>
-      <c r="E2" s="313" t="inlineStr">
-        <is>
-          <t>Điểm khối lượng</t>
-        </is>
-      </c>
-      <c r="F2" s="313" t="inlineStr">
-        <is>
-          <t>Ghi chú / lý do loại trừ</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="D3" s="314" t="n"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="314" t="n"/>
-    </row>
-    <row r="5" ht="28.5" customHeight="1">
-      <c r="A5" s="4" t="n"/>
-      <c r="B5" s="2" t="n"/>
-      <c r="D5" s="314" t="n"/>
-    </row>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="C3:C300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Cam kết,Phát sinh,Ngoài phạm vi"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>